--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -668,15 +668,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -725,15 +725,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A18,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A18,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A18,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A18,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A18,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A18,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -748,15 +748,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A19,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A19,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A19,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A19,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A19,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A19,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -771,15 +771,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A20,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A20,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A20,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A20,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A20,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A20,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -794,15 +794,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A21,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A21,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A21,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A21,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A21,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A21,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -817,15 +817,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A22,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A22,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A22,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A22,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A22,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A22,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -840,15 +840,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A23,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A23,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A23,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A23,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A23,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A23,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -863,15 +863,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A24,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A24,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A24,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A24,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A24,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A24,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -886,15 +886,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A25,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A25,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A25,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A25,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A25,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A25,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -909,15 +909,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A26,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A26,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A26,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A26,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A26,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A26,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A27,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A27,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A27,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A27,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A27,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A27,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -955,15 +955,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A28,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A28,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A28,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A28,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A28,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A28,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -978,15 +978,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A29,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A29,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A29,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A29,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A29,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A29,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1001,15 +1001,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A30,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A30,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A30,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A30,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A30,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A30,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1024,15 +1024,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A31,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A31,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A31,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A31,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A31,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A31,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1047,15 +1047,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A32,Tasks!$D$2:$D$85,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A32,Tasks!$D$2:$D$88,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A32,Tasks!$D$2:$D$85,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A32,Tasks!$D$2:$D$88,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$85,$A32,Tasks!$D$2:$D$85,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$88,$A32,Tasks!$D$2:$D$88,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1913,18 +1913,18 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>One-click 'request missing document' email to borrower</t>
+          <t>Requested-amount affordability check (auto-loan, personal-loan, small-business-loan)</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr"/>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>See Section 13 for the fuller self-service re-request concept from pain-point research</t>
+          <t>New — compares requestedAmount against a simplified income/revenue-based estimate; flags as Warning, never auto-declines. Not a real credit/DSCR calculation</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
+          <t>Warning-level flags surface at the application list level, not just inside document detail</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="E34" s="16" t="inlineStr"/>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>services/rag.js</t>
+          <t>Fixed today — routes/documents.js previously only bumped application status to Needs Review on a hard Mismatch, so an affordability warning was invisible in the officer's list view</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Citation / source attribution on every answer</t>
+          <t>US currency formatting fixed regardless of server/browser locale</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -1974,7 +1974,11 @@
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr"/>
-      <c r="F35" s="17" t="inlineStr"/>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>toLocaleString() was rendering $3,40,000-style grouping on non-US locales; forced to 'en-US' across backend and frontend</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="13" t="n">
@@ -1982,21 +1986,25 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Role-aware answers (officer vs. borrower)</t>
+          <t>One-click 'request missing document' email to borrower</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr"/>
-      <c r="F36" s="17" t="inlineStr"/>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>See Section 13 for the fuller self-service re-request concept from pain-point research</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="13" t="n">
@@ -2009,7 +2017,7 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
+          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -2020,7 +2028,7 @@
       <c r="E37" s="16" t="inlineStr"/>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>Validated in data/seed/test-questions.md</t>
+          <t>services/rag.js</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2043,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Small-business loan Q&amp;A coverage</t>
+          <t>Citation / source attribution on every answer</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -2044,11 +2052,7 @@
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr"/>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>test-questions.md items 19-23</t>
-        </is>
-      </c>
+      <c r="F38" s="17" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="13" t="n">
@@ -2061,20 +2065,16 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>WhatsApp channel for the assistant</t>
+          <t>Role-aware answers (officer vs. borrower)</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr"/>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>See Section 9</t>
-        </is>
-      </c>
+      <c r="F39" s="17" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -2087,18 +2087,18 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
+          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr"/>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>Recommended add-on from pain-point research — not yet scoped</t>
+          <t>Validated in data/seed/test-questions.md</t>
         </is>
       </c>
     </row>
@@ -2113,18 +2113,18 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Embeddings + vector search (scale-up path)</t>
+          <t>Small-business loan Q&amp;A coverage</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr"/>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
+          <t>test-questions.md items 19-23</t>
         </is>
       </c>
     </row>
@@ -2134,23 +2134,23 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Navigation shell (auth-gated stack navigation)</t>
+          <t>WhatsApp channel for the assistant</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr"/>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>App.js</t>
+          <t>See Section 9</t>
         </is>
       </c>
     </row>
@@ -2160,21 +2160,25 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Login screen</t>
+          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr"/>
-      <c r="F43" s="17" t="inlineStr"/>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>Recommended add-on from pain-point research — not yet scoped</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="13" t="n">
@@ -2182,23 +2186,23 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Applications list screen</t>
+          <t>Embeddings + vector search (scale-up path)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr"/>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>Officer sees all; borrower sees only their own</t>
+          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Application detail screen (header facts + tab bar)</t>
+          <t>Navigation shell (auth-gated stack navigation)</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -2224,7 +2228,7 @@
       <c r="E45" s="16" t="inlineStr"/>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>Branches fact display by product type</t>
+          <t>App.js</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Documents tab — upload + extracted fields display</t>
+          <t>Login screen</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -2261,7 +2265,7 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Verification tab — checks + missing documents</t>
+          <t>Applications list screen</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -2270,7 +2274,11 @@
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr"/>
-      <c r="F47" s="17" t="inlineStr"/>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>Officer sees all; borrower sees only their own</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="13" t="n">
@@ -2283,7 +2291,7 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Assistant tab — chat UI with source chips</t>
+          <t>Application detail screen (header facts + tab bar)</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -2292,7 +2300,11 @@
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr"/>
-      <c r="F48" s="17" t="inlineStr"/>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>Branches fact display by product type</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -2305,7 +2317,7 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Small-business-specific detail view (business name / revenue facts)</t>
+          <t>Documents tab — upload + extracted fields display</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
@@ -2327,7 +2339,7 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Fintech-styled visual design pass</t>
+          <t>Verification tab — checks + missing documents</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
@@ -2336,11 +2348,7 @@
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr"/>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>Per recent commit history</t>
-        </is>
-      </c>
+      <c r="F50" s="17" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="13" t="n">
@@ -2348,12 +2356,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus — 6 markdown policies</t>
+          <t>Assistant tab — chat UI with source chips</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
@@ -2362,11 +2370,7 @@
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr"/>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
-        </is>
-      </c>
+      <c r="F51" s="17" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="13" t="n">
@@ -2374,12 +2378,12 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Small Business Loan Requirements policy</t>
+          <t>Small-business-specific detail view (business name / revenue facts)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
@@ -2388,11 +2392,7 @@
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr"/>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>data/policies/small-business-loan-requirements.md</t>
-        </is>
-      </c>
+      <c r="F52" s="17" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
+          <t>Fintech-styled visual design pass</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -2416,7 +2416,7 @@
       <c r="E53" s="16" t="inlineStr"/>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
+          <t>Per recent commit history</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
+          <t>Policy corpus — 6 markdown policies</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -2442,7 +2442,7 @@
       <c r="E54" s="16" t="inlineStr"/>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
+          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Test question bank (acceptance checklist)</t>
+          <t>Small Business Loan Requirements policy</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -2468,7 +2468,7 @@
       <c r="E55" s="16" t="inlineStr"/>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
+          <t>data/policies/small-business-loan-requirements.md</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Demo script</t>
+          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -2494,7 +2494,7 @@
       <c r="E56" s="16" t="inlineStr"/>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
+          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
         </is>
       </c>
     </row>
@@ -2504,23 +2504,23 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Meta developer app + free sandbox test number</t>
+          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr"/>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>Self-serve, free, no leadership approval needed for the demo</t>
+          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
         </is>
       </c>
     </row>
@@ -2530,21 +2530,25 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
+          <t>Test question bank (acceptance checklist)</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr"/>
-      <c r="F58" s="17" t="inlineStr"/>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="13" t="n">
@@ -2552,23 +2556,23 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>Route inbound messages into the existing RAG assistant</t>
+          <t>Demo script</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr"/>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>Can reuse services/rag.js — answerQuestion()</t>
+          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2587,7 @@
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Outbound reply via WhatsApp Cloud API</t>
+          <t>Meta developer app + free sandbox test number</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
@@ -2592,7 +2596,11 @@
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr"/>
-      <c r="F60" s="17" t="inlineStr"/>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>Self-serve, free, no leadership approval needed for the demo</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="13" t="n">
@@ -2605,7 +2613,7 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Production Meta Business verification</t>
+          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
@@ -2614,11 +2622,7 @@
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr"/>
-      <c r="F61" s="17" t="inlineStr">
-        <is>
-          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
-        </is>
-      </c>
+      <c r="F61" s="17" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="13" t="n">
@@ -2626,23 +2630,23 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Render Blueprint configuration</t>
+          <t>Route inbound messages into the existing RAG assistant</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr"/>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>render.yaml — backend web service + frontend static site</t>
+          <t>Can reuse services/rag.js — answerQuestion()</t>
         </is>
       </c>
     </row>
@@ -2652,25 +2656,21 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Backend deployed &amp; health-checked on Render</t>
+          <t>Outbound reply via WhatsApp Cloud API</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr"/>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>Confirm live and reachable before demo day (/health)</t>
-        </is>
-      </c>
+      <c r="F63" s="17" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="13" t="n">
@@ -2678,23 +2678,23 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Frontend deployed as Render static site</t>
+          <t>Production Meta Business verification</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr"/>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Confirm Expo web export + rewrite rule are working</t>
+          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
         </is>
       </c>
     </row>
@@ -2709,18 +2709,18 @@
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
+          <t>Render Blueprint configuration</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E65" s="16" t="inlineStr"/>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
+          <t>render.yaml — backend web service + frontend static site</t>
         </is>
       </c>
     </row>
@@ -2735,18 +2735,18 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
+          <t>Backend deployed &amp; health-checked on Render</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr"/>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+          <t>Confirm live and reachable before demo day (/health)</t>
         </is>
       </c>
     </row>
@@ -2756,23 +2756,23 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Manual acceptance test question bank</t>
+          <t>Frontend deployed as Render static site</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E67" s="16" t="inlineStr"/>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>23 questions across consumer + small-business scenarios</t>
+          <t>Confirm Expo web export + rewrite rule are working</t>
         </is>
       </c>
     </row>
@@ -2782,21 +2782,25 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Automated unit/integration tests</t>
+          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E68" s="16" t="inlineStr"/>
-      <c r="F68" s="17" t="inlineStr"/>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="13" t="n">
@@ -2804,23 +2808,23 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>End-to-end demo rehearsal (full run-through, timed)</t>
+          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E69" s="16" t="inlineStr"/>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>Schedule before presentation day</t>
+          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
         </is>
       </c>
     </row>
@@ -2835,16 +2839,20 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Cross-browser / device check (Expo web export)</t>
+          <t>Manual acceptance test question bank</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E70" s="16" t="inlineStr"/>
-      <c r="F70" s="17" t="inlineStr"/>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>23 questions across consumer + small-business scenarios</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="13" t="n">
@@ -2852,17 +2860,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>README (quick start, architecture, deploy steps)</t>
+          <t>Automated unit/integration tests</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E71" s="16" t="inlineStr"/>
@@ -2874,21 +2882,25 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>ROADMAP.md (phased build plan)</t>
+          <t>End-to-end demo rehearsal (full run-through, timed)</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr"/>
-      <c r="F72" s="17" t="inlineStr"/>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>Schedule before presentation day</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="13" t="n">
@@ -2896,17 +2908,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
+          <t>Cross-browser / device check (Expo web export)</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr"/>
@@ -2923,7 +2935,7 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Development task tracker (this file)</t>
+          <t>README (quick start, architecture, deploy steps)</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -2932,11 +2944,7 @@
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr"/>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
-        </is>
-      </c>
+      <c r="F74" s="17" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="13" t="n">
@@ -2944,25 +2952,21 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>In-browser instant document classification &amp; quality check at upload</t>
+          <t>ROADMAP.md (phased build plan)</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr"/>
-      <c r="F75" s="17" t="inlineStr">
-        <is>
-          <t>Runs the existing extraction before submission instead of after, with immediate feedback</t>
-        </is>
-      </c>
+      <c r="F75" s="17" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="13" t="n">
@@ -2970,25 +2974,21 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Pre-submission completeness check (required schedules/pages present)</t>
+          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr"/>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>Per document type</t>
-        </is>
-      </c>
+      <c r="F76" s="17" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="13" t="n">
@@ -2996,23 +2996,23 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Blur / glare / legibility detection before accepting an upload</t>
+          <t>Development task tracker (this file)</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>Complements existing confidence-score routing in verification.js</t>
+          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Self-service secure re-upload link (SMS / magic link) on document rejection</t>
+          <t>In-browser instant document classification &amp; quality check at upload</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -3038,7 +3038,7 @@
       <c r="E78" s="16" t="inlineStr"/>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>Directly answers the #1 pain point from Rovo research — 'document ping-pong' / stuck Needs-Review workflows</t>
+          <t>Runs the existing extraction before submission instead of after, with immediate feedback</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+          <t>Pre-submission completeness check (required schedules/pages present)</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
@@ -3064,7 +3064,7 @@
       <c r="E79" s="16" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+          <t>Per document type</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+          <t>Blur / glare / legibility detection before accepting an upload</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
@@ -3090,7 +3090,7 @@
       <c r="E80" s="16" t="inlineStr"/>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>Complements existing confidence-score routing in verification.js</t>
         </is>
       </c>
     </row>
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+          <t>Self-service secure re-upload link (SMS / magic link) on document rejection</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="E81" s="16" t="inlineStr"/>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+          <t>Directly answers the #1 pain point from Rovo research — 'document ping-pong' / stuck Needs-Review workflows</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Shared visibility for all parties on one application</t>
+          <t>Auto pre-fill of underwriting review fields from extracted data</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
@@ -3142,7 +3142,7 @@
       <c r="E82" s="16" t="inlineStr"/>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>Requires multi-user access to a single application — auth model currently ties an application to one applicant email</t>
+          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
@@ -3168,7 +3168,7 @@
       <c r="E83" s="16" t="inlineStr"/>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
@@ -3194,7 +3194,7 @@
       <c r="E84" s="16" t="inlineStr"/>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Self-service grace period / split-payment offers</t>
+          <t>Shared visibility for all parties on one application</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
@@ -3220,13 +3220,91 @@
       <c r="E85" s="16" t="inlineStr"/>
       <c r="F85" s="17" t="inlineStr">
         <is>
+          <t>Requires multi-user access to a single application — auth model currently ties an application to one applicant email</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr"/>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="inlineStr"/>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Self-service grace period / split-payment offers</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr"/>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F85"/>
-  <conditionalFormatting sqref="D2:D85">
+  <autoFilter ref="A1:F88"/>
+  <conditionalFormatting sqref="D2:D88">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -3238,7 +3316,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +91,12 @@
       <color rgb="000A2540"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00667085"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -129,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,11 +180,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -210,6 +221,27 @@
         <color rgb="00475467"/>
         <sz val="10"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F1F5F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F1F5F9"/>
@@ -668,15 +700,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -725,15 +757,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A18,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A18,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A18,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A18,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A18,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A18,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -748,15 +780,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A19,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A19,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A19,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A19,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A19,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A19,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -771,15 +803,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A20,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A20,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A20,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A20,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A20,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A20,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -794,15 +826,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A21,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A21,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A21,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A21,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A21,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A21,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -817,15 +849,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A22,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A22,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A22,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A22,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A22,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A22,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -840,15 +872,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A23,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A23,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A23,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A23,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A23,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A23,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -863,15 +895,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A24,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A24,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A24,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A24,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A24,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A24,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -886,15 +918,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A25,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A25,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A25,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A25,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A25,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A25,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -909,15 +941,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A26,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A26,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A26,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A26,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A26,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A26,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -932,15 +964,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A27,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A27,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A27,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A27,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A27,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A27,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -955,15 +987,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A28,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A28,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A28,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A28,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A28,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A28,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -978,15 +1010,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A29,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A29,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A29,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A29,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A29,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A29,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1001,15 +1033,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A30,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A30,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A30,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A30,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A30,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A30,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1024,15 +1056,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A31,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A31,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A31,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A31,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A31,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A31,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1047,15 +1079,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A32,Tasks!$D$2:$D$88,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A32,Tasks!$D$2:$D$94,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A32,Tasks!$D$2:$D$88,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A32,Tasks!$D$2:$D$94,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$88,$A32,Tasks!$D$2:$D$88,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$94,$A32,Tasks!$D$2:$D$94,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1077,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1996,13 +2028,13 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr"/>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>See Section 13 for the fuller self-service re-request concept from pain-point research</t>
+          <t>Superseded by the richer in-app live-exception + targeted self-service re-upload flow — see Section 13. No email/SMS needed; the borrower sees and fixes it directly in the app</t>
         </is>
       </c>
     </row>
@@ -3027,18 +3059,18 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>In-browser instant document classification &amp; quality check at upload</t>
+          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr"/>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>Runs the existing extraction before submission instead of after, with immediate feedback</t>
+          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
         </is>
       </c>
     </row>
@@ -3053,18 +3085,18 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Pre-submission completeness check (required schedules/pages present)</t>
+          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>Per document type</t>
+          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
         </is>
       </c>
     </row>
@@ -3079,18 +3111,18 @@
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Blur / glare / legibility detection before accepting an upload</t>
+          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr"/>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>Complements existing confidence-score routing in verification.js</t>
+          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
         </is>
       </c>
     </row>
@@ -3105,18 +3137,18 @@
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Self-service secure re-upload link (SMS / magic link) on document rejection</t>
+          <t>Document supersede/audit-trail model (current vs. superseded)</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr"/>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>Directly answers the #1 pain point from Rovo research — 'document ping-pong' / stuck Needs-Review workflows</t>
+          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
         </is>
       </c>
     </row>
@@ -3131,18 +3163,18 @@
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr"/>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
         </is>
       </c>
     </row>
@@ -3152,23 +3184,23 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr"/>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
         </is>
       </c>
     </row>
@@ -3178,23 +3210,23 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+          <t>RAG assistant reflects only current, unresolved exceptions</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr"/>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3236,12 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Shared visibility for all parties on one application</t>
+          <t>In-browser instant document classification &amp; quality check at upload</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
@@ -3220,7 +3252,7 @@
       <c r="E85" s="16" t="inlineStr"/>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>Requires multi-user access to a single application — auth model currently ties an application to one applicant email</t>
+          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3262,12 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+          <t>Pre-submission completeness check (required schedules/pages present)</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
@@ -3246,7 +3278,7 @@
       <c r="E86" s="16" t="inlineStr"/>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+          <t>Per document type</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3288,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+          <t>Blur / glare / legibility detection before accepting an upload</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
@@ -3272,7 +3304,7 @@
       <c r="E87" s="16" t="inlineStr"/>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+          <t>Complements existing confidence-score routing in verification.js</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3314,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Self-service grace period / split-payment offers</t>
+          <t>Auto pre-fill of underwriting review fields from extracted data</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
@@ -3298,13 +3330,169 @@
       <c r="E88" s="16" t="inlineStr"/>
       <c r="F88" s="17" t="inlineStr">
         <is>
+          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr"/>
+      <c r="F89" s="17" t="inlineStr">
+        <is>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="13" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr"/>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>Shared visibility for all parties on one application</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="inlineStr"/>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr"/>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="inlineStr"/>
+      <c r="F93" s="17" t="inlineStr">
+        <is>
+          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Self-service grace period / split-payment offers</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr"/>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F88"/>
-  <conditionalFormatting sqref="D2:D88">
+  <autoFilter ref="A1:F94"/>
+  <conditionalFormatting sqref="D2:D94">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -3316,10 +3504,607 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Feature Area</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Steps to Test</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Why This Matters (Use Case &amp; Impact)</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Verified So Far</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Affordability check</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Auto/personal loan requested amount within the estimated affordable range</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Upload a pay stub where documented income comfortably supports the requested amount.</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>'Requested amount vs. affordability' check shows status Match — no flag.</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Confirms the check doesn't cry wolf on ordinary, reasonable requests — false positives would erode officer trust in every other flag the system raises.</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Affordability check</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Auto/personal loan requested amount exceeds the estimate</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Upload a pay stub where documented income is well below what the requested amount implies.</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Status Warning (not a hard decline), names the multiple over (e.g. '3.1x'), suggests checking for a data-entry error, and the application still requires officer sign-off.</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>This is the gap that existed before today's session: nothing previously checked requested amount against income at all. Officers can now triage oversized asks instead of discovering them deep in manual underwriting.</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Affordability check</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Combined income mismatch + oversized request (worse-case)</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Pay stub shows both a different income than stated AND a requested amount unaffordable even at the (lower) documented income.</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Both checks fire independently; overall status is 'fail' (hard mismatch outranks a warning) — the more serious problem wins the overall severity.</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Confirms severity ranking is sane: a data conflict (documents disagree) is treated as more serious than a disproportionate-but-consistent request, so officers aren't misled about which case is more urgent.</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Affordability check</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Extreme, isolated oversized request ($500/mo income, $5,000,000 requested)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Income confirmed correct and consistent; only the requested amount is absurd.</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Overall status is 'needs-review', not 'fail' — distinguishing 'plausible but oversized' from 'documents disagree'. Explanation states the request is ~617x the affordable estimate.</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>This is the exact scenario raised in planning: proves the system never auto-declines, always routes to a human, and gives the officer enough context (the multiple) to spot a likely typo instantly instead of investigating from scratch.</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Affordability check</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Small-business flagship scenario (Whitfield &amp; Co. Bakery LLC)</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Run the seeded small-business application: tax return shows $275,400 revenue vs. $340,000 stated, business license shows a different legal name, and $110,000 is requested.</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Three independent flags appear together — revenue mismatch, business-name mismatch, and affordability (~1.3x over) — each with its own plain-English explanation.</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>This is the demo's core evidence that the engine catches the real, evidence-backed pain points (entity-name mismatches, revenue verification) found in production loan-servicing research, not hypothetical ones.</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>US currency formatting is locale-independent</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Run any check that renders a dollar amount on a machine/browser set to a non-US locale.</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Amounts render as '$340,000' (US grouping), never '$3,40,000' or similar.</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Caught during this session's own testing — would have looked broken live in front of judges depending on whoever's laptop or browser locale was in use, undermining credibility for reasons having nothing to do with the actual feature.</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>A flagged document appears in the borrower's/officer's 'Action needed' list</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Upload a document that fails a check (e.g. Jordan Rivera's pay stub, planted income mismatch).</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Documents tab shows an 'Action needed' card naming the specific issue in plain language, with a Re-upload button.</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Replaces 'the flag exists somewhere in a Verification tab, hope someone notices' with one obvious, actionable place — this is the core of the 'live exception' pitch.</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Partial — core logic simulated in Node standalone; full Express+MongoDB route not executed (no local .env/API key in this environment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Targeted re-upload resolves exactly one exception</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Tap Re-upload on one flagged item and upload a corrected document.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>That exception disappears from the Action needed list; other open exceptions (if any) are untouched.</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>This is the 'minutes not days' claim made concrete — no email, no waiting for an officer to notice, no restarting the application.</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Partial — core logic simulated in Node standalone; full Express+MongoDB route not executed (no local .env/API key in this environment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Wrong file type caught immediately during a targeted fix</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>While fixing a specific required item (e.g. Driver's License), upload an unrelated document type (e.g. a bank statement).</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>A 'Document type' mismatch appears immediately, naming both the expected and actual type — not a silent or confusing failure.</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Prevents a second round of 'document ping-pong' from being reintroduced by the fix mechanism itself — the applicant knows right away, not after another review cycle.</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>A wrong-type attempt doesn't linger as an orphaned exception</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Immediately follow the previous scenario with the correct document type for that same slot.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>The earlier wrong-type attempt is superseded (marked historical), not left behind as a second, permanent exception with no way to resolve it.</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>This was an actual bug found and fixed during this session's own testing before shipping — without the fix, a single wrong upload would have permanently cluttered the exception list with no way to clear it.</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Application status self-heals once every exception clears</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Resolve the last open exception on an application that was in 'Needs Review'.</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Application status automatically returns to 'Submitted' — no officer action required to remove a flag that no longer applies.</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Closes the loop end-to-end: today, even after a borrower fixes something, an officer typically has to notice and manually clear the flag. This makes the fix instantly visible everywhere the status is shown.</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Superseded documents are preserved for audit but hidden from the active view</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>After a targeted fix, open 'Show document history' on the Documents tab.</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>The old (fixed) document appears there, clearly marked 'Superseded', separate from the current, active document list.</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Keeps the 'complete audit trail' claim in the original pitch true even as documents get corrected — nothing is silently deleted.</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>RAG assistant never re-surfaces a resolved issue</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>After resolving all exceptions, ask the assistant (as officer) 'why is this application flagged?'</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>The assistant does not reference the earlier, now-fixed issue — its context reflects only current, unresolved state.</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Caught during this session's review: the assistant was reading ALL documents including superseded ones, so a fixed issue could be wrongly explained as still open — directly undermines trust in the assistant if a judge or officer notices it.</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>A borrower cannot upload to another applicant's application</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>As an authenticated borrower, attempt to POST a document to an applicationId that isn't theirs.</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>403 'Not your application'. An officer performing the same action is unaffected.</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Caught during this session's own review: the upload endpoint had no ownership check at all before today, unlike the equivalent read endpoint — a real gap for a feature whose whole point is borrower self-service.</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Live exception flow</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Officer and borrower see the identical live exception list</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Compare the Documents tab for the same application, once logged in as officer and once as the borrower.</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Both show the exact same 'Action needed' items — same wording, same count.</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Directly closes the 'black box' gap found in pain-point research, where today the officer's dashboard and the borrower's visibility can drift apart with no shared source of truth.</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G16"/>
+  <conditionalFormatting sqref="G2:G16">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>LEFT($G2,3)="Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="4">
+      <formula>LEFT($G2,7)="Partial"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>LEFT($G2,7)="Not yet"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -700,15 +700,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -757,15 +757,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A18,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A18,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A18,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A18,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A18,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A18,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -780,15 +780,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A19,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A19,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A19,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A19,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A19,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A19,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -803,15 +803,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A20,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A20,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A20,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A20,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A20,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A20,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -826,15 +826,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A21,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A21,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A21,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A21,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A21,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A21,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -849,15 +849,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A22,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A22,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A22,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A22,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A22,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A22,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -872,15 +872,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A23,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A23,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A23,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A23,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A23,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A23,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -895,15 +895,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A24,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A24,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A24,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A24,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A24,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A24,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -918,15 +918,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A25,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A25,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A25,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A25,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A25,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A25,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -941,15 +941,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A26,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A26,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A26,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A26,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A26,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A26,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -964,15 +964,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A27,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A27,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A27,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A27,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A27,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A27,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -987,15 +987,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A28,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A28,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A28,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A28,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A28,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A28,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1010,15 +1010,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A29,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A29,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A29,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A29,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A29,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A29,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A30,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A30,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A30,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A30,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A30,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A30,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1056,15 +1056,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A31,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A31,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A31,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A31,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A31,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A31,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1079,15 +1079,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A32,Tasks!$D$2:$D$94,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A32,Tasks!$D$2:$D$104,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A32,Tasks!$D$2:$D$94,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A32,Tasks!$D$2:$D$104,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$94,$A32,Tasks!$D$2:$D$94,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$104,$A32,Tasks!$D$2:$D$104,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1109,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1397,18 +1397,18 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Password reset / self-service registration</t>
+          <t>Self-service registration (POST /auth/register)</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr"/>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>Out of scope for demo — seeded demo accounts only</t>
+          <t>No email verification — synthetic-data demo, not real bank onboarding. Lets teammates spin up their own officer/borrower test accounts instead of needing seeded ones</t>
         </is>
       </c>
     </row>
@@ -1418,23 +1418,23 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>3. Data Model &amp; Database (MongoDB)</t>
+          <t>2. Authentication &amp; Access Control</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>MongoDB Atlas connection (Mongoose)</t>
+          <t>Password reset</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr"/>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>backend/src/config/db.js</t>
+          <t>Out of scope for demo</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>User model</t>
+          <t>MongoDB Atlas connection (Mongoose)</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -1460,7 +1460,7 @@
       <c r="E13" s="16" t="inlineStr"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>models/User.js</t>
+          <t>backend/src/config/db.js</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Application model</t>
+          <t>User model</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -1486,7 +1486,7 @@
       <c r="E14" s="16" t="inlineStr"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Supports auto-loan, personal-loan, small-business-loan — models/Application.js</t>
+          <t>models/User.js</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Document model (upload + verification results)</t>
+          <t>Application model</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -1512,7 +1512,7 @@
       <c r="E15" s="16" t="inlineStr"/>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>models/Document.js</t>
+          <t>Supports auto-loan, personal-loan, small-business-loan — models/Application.js</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>PolicyChunk model (RAG corpus storage)</t>
+          <t>Document model (upload + verification results)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
@@ -1538,7 +1538,7 @@
       <c r="E16" s="16" t="inlineStr"/>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>models/PolicyChunk.js</t>
+          <t>models/Document.js</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Seed script — demo users &amp; applications</t>
+          <t>PolicyChunk model (RAG corpus storage)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -1564,7 +1564,7 @@
       <c r="E17" s="16" t="inlineStr"/>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>scripts/seed.js — extended with the small-business scenario</t>
+          <t>models/PolicyChunk.js</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Policy ingestion script (chunks policy markdown into PolicyChunk)</t>
+          <t>Seed script — demo users &amp; applications</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -1590,7 +1590,7 @@
       <c r="E18" s="16" t="inlineStr"/>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>scripts/ingestPolicies.js</t>
+          <t>scripts/seed.js — extended with the small-business scenario</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>4. Document Intelligence (OCR / AI Extraction)</t>
+          <t>3. Data Model &amp; Database (MongoDB)</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Claude vision classify + extract (single API call, no separate OCR service)</t>
+          <t>Policy ingestion script (chunks policy markdown into PolicyChunk)</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -1616,7 +1616,7 @@
       <c r="E19" s="16" t="inlineStr"/>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>services/extraction.js</t>
+          <t>scripts/ingestPolicies.js</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>4. Document Intelligence (OCR / AI Extraction)</t>
+          <t>3. Data Model &amp; Database (MongoDB)</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Consumer document types — pay stub, W-2, bank statement, driver's license</t>
+          <t>Borrower self-service loan application intake (POST /applications)</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -1640,7 +1640,11 @@
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="17" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>A registered borrower can apply for a loan directly — sets requiredDocTypes from the shared config, borrower-only (officers don't file applications for themselves here)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="13" t="n">
@@ -1648,12 +1652,12 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>4. Document Intelligence (OCR / AI Extraction)</t>
+          <t>3. Data Model &amp; Database (MongoDB)</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Small-business document types — tax return, personal financial statement, business license, ownership disclosure</t>
+          <t>Shared required-documents config (dedupe)</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -1664,7 +1668,7 @@
       <c r="E21" s="16" t="inlineStr"/>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>extraction.js prompt + fields extended</t>
+          <t>config/requiredDocs.js — was duplicated across seed.js and admin.js; now also used by the new application-intake route</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1678,12 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>4. Document Intelligence (OCR / AI Extraction)</t>
+          <t>3. Data Model &amp; Database (MongoDB)</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Document upload endpoint (multer, 10MB limit)</t>
+          <t>Dana Whitfield borrower login added to seed data</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
@@ -1690,7 +1694,7 @@
       <c r="E22" s="16" t="inlineStr"/>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>routes/documents.js</t>
+          <t>So the small-business flagship scenario can be demoed as an actual borrower self-service session, not just via the officer login</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1704,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>4. Document Intelligence (OCR / AI Extraction)</t>
+          <t>3. Data Model &amp; Database (MongoDB)</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Confidence scoring + low-confidence to human review routing</t>
+          <t>Date of birth + 18-or-older check on application intake</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -1716,7 +1720,7 @@
       <c r="E23" s="16" t="inlineStr"/>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>services/verification.js</t>
+          <t>Grounded in Rovo research on Apiture's real DAO intake flow — every product policy already stated '18 or older' but nothing checked it, since there was no DOB field at all before this</t>
         </is>
       </c>
     </row>
@@ -1726,23 +1730,23 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>4. Document Intelligence (OCR / AI Extraction)</t>
+          <t>3. Data Model &amp; Database (MongoDB)</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Extraction accuracy tuning against real-world-style documents</t>
+          <t>E-sign / credit-pull consent capture on application intake</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr"/>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Only validated against synthetic generated images so far</t>
+          <t>consentAcceptedAt on Application — matches the 'Disclosures &amp; Submit' step found in every real DAO intake flow Rovo surfaced</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1756,12 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Deterministic rule engine (not LLM — explainable/auditable)</t>
+          <t>Claude vision classify + extract (single API call, no separate OCR service)</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -1768,7 +1772,7 @@
       <c r="E25" s="16" t="inlineStr"/>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>services/verification.js</t>
+          <t>services/extraction.js</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1782,12 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Name match check</t>
+          <t>Consumer document types — pay stub, W-2, bank statement, driver's license</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -1800,12 +1804,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Income match check (5% tolerance)</t>
+          <t>Small-business document types — tax return, personal financial statement, business license, ownership disclosure</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -1814,7 +1818,11 @@
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr"/>
-      <c r="F27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>extraction.js prompt + fields extended</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="13" t="n">
@@ -1822,12 +1830,12 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Employer match check</t>
+          <t>Document upload endpoint (multer, 10MB limit)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -1836,7 +1844,11 @@
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr"/>
-      <c r="F28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>routes/documents.js</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="13" t="n">
@@ -1844,12 +1856,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>SSN (last 4) match check</t>
+          <t>Confidence scoring + low-confidence to human review routing</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -1858,7 +1870,11 @@
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr"/>
-      <c r="F29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>services/verification.js</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="13" t="n">
@@ -1866,23 +1882,23 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Business name / DBA match check</t>
+          <t>Extraction accuracy tuning against real-world-style documents</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr"/>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Demonstrates the entity-name-mismatch pattern found in production loan-servicing tickets</t>
+          <t>Only validated against synthetic generated images so far</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1913,7 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Annual business revenue match check</t>
+          <t>Deterministic rule engine (not LLM — explainable/auditable)</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -1906,7 +1922,11 @@
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr"/>
-      <c r="F31" s="17" t="inlineStr"/>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>services/verification.js</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="n">
@@ -1919,7 +1939,7 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Missing-document detection</t>
+          <t>Name match check</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -1928,11 +1948,7 @@
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr"/>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>missingDocuments() in verification.js</t>
-        </is>
-      </c>
+      <c r="F32" s="17" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="13" t="n">
@@ -1945,7 +1961,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Requested-amount affordability check (auto-loan, personal-loan, small-business-loan)</t>
+          <t>Income match check (5% tolerance)</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
@@ -1954,11 +1970,7 @@
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr"/>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>New — compares requestedAmount against a simplified income/revenue-based estimate; flags as Warning, never auto-declines. Not a real credit/DSCR calculation</t>
-        </is>
-      </c>
+      <c r="F33" s="17" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="13" t="n">
@@ -1971,7 +1983,7 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Warning-level flags surface at the application list level, not just inside document detail</t>
+          <t>Employer match check</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -1980,11 +1992,7 @@
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr"/>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>Fixed today — routes/documents.js previously only bumped application status to Needs Review on a hard Mismatch, so an affordability warning was invisible in the officer's list view</t>
-        </is>
-      </c>
+      <c r="F34" s="17" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="13" t="n">
@@ -1997,7 +2005,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>US currency formatting fixed regardless of server/browser locale</t>
+          <t>SSN (last 4) match check</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -2006,11 +2014,7 @@
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr"/>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>toLocaleString() was rendering $3,40,000-style grouping on non-US locales; forced to 'en-US' across backend and frontend</t>
-        </is>
-      </c>
+      <c r="F35" s="17" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="13" t="n">
@@ -2023,7 +2027,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>One-click 'request missing document' email to borrower</t>
+          <t>Business name / DBA match check</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
@@ -2034,7 +2038,7 @@
       <c r="E36" s="16" t="inlineStr"/>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>Superseded by the richer in-app live-exception + targeted self-service re-upload flow — see Section 13. No email/SMS needed; the borrower sees and fixes it directly in the app</t>
+          <t>Demonstrates the entity-name-mismatch pattern found in production loan-servicing tickets</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2048,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
+          <t>Annual business revenue match check</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -2058,11 +2062,7 @@
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr"/>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>services/rag.js</t>
-        </is>
-      </c>
+      <c r="F37" s="17" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Citation / source attribution on every answer</t>
+          <t>Missing-document detection</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -2084,7 +2084,11 @@
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr"/>
-      <c r="F38" s="17" t="inlineStr"/>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>missingDocuments() in verification.js</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="13" t="n">
@@ -2092,12 +2096,12 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Role-aware answers (officer vs. borrower)</t>
+          <t>Requested-amount affordability check (auto-loan, personal-loan, small-business-loan)</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -2106,7 +2110,11 @@
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr"/>
-      <c r="F39" s="17" t="inlineStr"/>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>New — compares requestedAmount against a simplified income/revenue-based estimate; flags as Warning, never auto-declines. Not a real credit/DSCR calculation</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -2114,12 +2122,12 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
+          <t>Warning-level flags surface at the application list level, not just inside document detail</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -2130,7 +2138,7 @@
       <c r="E40" s="16" t="inlineStr"/>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>Validated in data/seed/test-questions.md</t>
+          <t>Fixed today — routes/documents.js previously only bumped application status to Needs Review on a hard Mismatch, so an affordability warning was invisible in the officer's list view</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2148,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Small-business loan Q&amp;A coverage</t>
+          <t>US currency formatting fixed regardless of server/browser locale</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -2156,7 +2164,7 @@
       <c r="E41" s="16" t="inlineStr"/>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>test-questions.md items 19-23</t>
+          <t>toLocaleString() was rendering $3,40,000-style grouping on non-US locales; forced to 'en-US' across backend and frontend</t>
         </is>
       </c>
     </row>
@@ -2166,23 +2174,23 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>WhatsApp channel for the assistant</t>
+          <t>One-click 'request missing document' email to borrower</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr"/>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>See Section 9</t>
+          <t>Superseded by the richer in-app live-exception + targeted self-service re-upload flow — see Section 13. No email/SMS needed; the borrower sees and fixes it directly in the app</t>
         </is>
       </c>
     </row>
@@ -2197,18 +2205,18 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
+          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr"/>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>Recommended add-on from pain-point research — not yet scoped</t>
+          <t>services/rag.js</t>
         </is>
       </c>
     </row>
@@ -2223,20 +2231,16 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Embeddings + vector search (scale-up path)</t>
+          <t>Citation / source attribution on every answer</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr"/>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
-        </is>
-      </c>
+      <c r="F44" s="17" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="13" t="n">
@@ -2244,12 +2248,12 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Navigation shell (auth-gated stack navigation)</t>
+          <t>Role-aware answers (officer vs. borrower)</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -2258,11 +2262,7 @@
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr"/>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>App.js</t>
-        </is>
-      </c>
+      <c r="F45" s="17" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="13" t="n">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Login screen</t>
+          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -2284,7 +2284,11 @@
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr"/>
-      <c r="F46" s="17" t="inlineStr"/>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>Validated in data/seed/test-questions.md</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -2292,12 +2296,12 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Applications list screen</t>
+          <t>Small-business loan Q&amp;A coverage</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -2308,7 +2312,7 @@
       <c r="E47" s="16" t="inlineStr"/>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>Officer sees all; borrower sees only their own</t>
+          <t>test-questions.md items 19-23</t>
         </is>
       </c>
     </row>
@@ -2318,23 +2322,23 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Application detail screen (header facts + tab bar)</t>
+          <t>WhatsApp channel for the assistant</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr"/>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>Branches fact display by product type</t>
+          <t>See Section 9</t>
         </is>
       </c>
     </row>
@@ -2344,21 +2348,25 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Documents tab — upload + extracted fields display</t>
+          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr"/>
-      <c r="F49" s="17" t="inlineStr"/>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>Recommended add-on from pain-point research — not yet scoped</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="13" t="n">
@@ -2366,21 +2374,25 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Verification tab — checks + missing documents</t>
+          <t>Embeddings + vector search (scale-up path)</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr"/>
-      <c r="F50" s="17" t="inlineStr"/>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="13" t="n">
@@ -2393,7 +2405,7 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Assistant tab — chat UI with source chips</t>
+          <t>Navigation shell (auth-gated stack navigation)</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
@@ -2402,7 +2414,11 @@
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr"/>
-      <c r="F51" s="17" t="inlineStr"/>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>App.js</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="13" t="n">
@@ -2415,7 +2431,7 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Small-business-specific detail view (business name / revenue facts)</t>
+          <t>Login screen</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
@@ -2437,7 +2453,7 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Fintech-styled visual design pass</t>
+          <t>Applications list screen</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -2448,7 +2464,7 @@
       <c r="E53" s="16" t="inlineStr"/>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>Per recent commit history</t>
+          <t>Officer sees all; borrower sees only their own</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2474,12 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus — 6 markdown policies</t>
+          <t>Application detail screen (header facts + tab bar)</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -2474,7 +2490,7 @@
       <c r="E54" s="16" t="inlineStr"/>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
+          <t>Branches fact display by product type</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2500,12 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Small Business Loan Requirements policy</t>
+          <t>Documents tab — upload + extracted fields display</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -2498,11 +2514,7 @@
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr"/>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>data/policies/small-business-loan-requirements.md</t>
-        </is>
-      </c>
+      <c r="F55" s="17" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="13" t="n">
@@ -2510,12 +2522,12 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
+          <t>Verification tab — checks + missing documents</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -2524,11 +2536,7 @@
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr"/>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
-        </is>
-      </c>
+      <c r="F56" s="17" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="13" t="n">
@@ -2536,12 +2544,12 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
+          <t>Assistant tab — chat UI with source chips</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -2550,11 +2558,7 @@
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr"/>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
-        </is>
-      </c>
+      <c r="F57" s="17" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="13" t="n">
@@ -2562,12 +2566,12 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Test question bank (acceptance checklist)</t>
+          <t>Small-business-specific detail view (business name / revenue facts)</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
@@ -2576,11 +2580,7 @@
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr"/>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
-        </is>
-      </c>
+      <c r="F58" s="17" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="13" t="n">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>Demo script</t>
+          <t>Fintech-styled visual design pass</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -2604,7 +2604,7 @@
       <c r="E59" s="16" t="inlineStr"/>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
+          <t>Per recent commit history</t>
         </is>
       </c>
     </row>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Meta developer app + free sandbox test number</t>
+          <t>Sign-up screen (self-registration, role picker)</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr"/>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>Self-serve, free, no leadership approval needed for the demo</t>
+          <t>SignUpScreen.js</t>
         </is>
       </c>
     </row>
@@ -2640,21 +2640,25 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
+          <t>New Application screen ('Apply for a Loan')</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr"/>
-      <c r="F61" s="17" t="inlineStr"/>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>NewApplicationScreen.js — product-type picker with conditional fields (consumer income/employer vs. business name/revenue), submits to POST /applications then lands on that application's Documents tab</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="13" t="n">
@@ -2662,23 +2666,23 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Route inbound messages into the existing RAG assistant</t>
+          <t>'New application' entry point on the borrower's Applications list</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr"/>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>Can reuse services/rag.js — answerQuestion()</t>
+          <t>Officer role doesn't see this button — they don't file applications for themselves</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2692,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Outbound reply via WhatsApp Cloud API</t>
+          <t>Multi-step wizard for the Apply form (Select Product -&gt; Your Info -&gt; Disclosures &amp; Submit)</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
@@ -2702,7 +2706,11 @@
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr"/>
-      <c r="F63" s="17" t="inlineStr"/>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>Currently one scrollable form. Real DAO intake flows are multi-step wizards with these exact section boundaries per Rovo research — a good polish pass, not done yet</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="13" t="n">
@@ -2710,23 +2718,23 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Production Meta Business verification</t>
+          <t>Policy corpus — 6 markdown policies</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr"/>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
+          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2744,12 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Render Blueprint configuration</t>
+          <t>Small Business Loan Requirements policy</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
@@ -2752,7 +2760,7 @@
       <c r="E65" s="16" t="inlineStr"/>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>render.yaml — backend web service + frontend static site</t>
+          <t>data/policies/small-business-loan-requirements.md</t>
         </is>
       </c>
     </row>
@@ -2762,23 +2770,23 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Backend deployed &amp; health-checked on Render</t>
+          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr"/>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>Confirm live and reachable before demo day (/health)</t>
+          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
         </is>
       </c>
     </row>
@@ -2788,23 +2796,23 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Frontend deployed as Render static site</t>
+          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E67" s="16" t="inlineStr"/>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>Confirm Expo web export + rewrite rule are working</t>
+          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
         </is>
       </c>
     </row>
@@ -2814,23 +2822,23 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
+          <t>Test question bank (acceptance checklist)</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E68" s="16" t="inlineStr"/>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
+          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2848,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
+          <t>Demo script</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
@@ -2856,7 +2864,7 @@
       <c r="E69" s="16" t="inlineStr"/>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
         </is>
       </c>
     </row>
@@ -2866,23 +2874,23 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Manual acceptance test question bank</t>
+          <t>Meta developer app + free sandbox test number</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E70" s="16" t="inlineStr"/>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>23 questions across consumer + small-business scenarios</t>
+          <t>Self-serve, free, no leadership approval needed for the demo</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2900,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Automated unit/integration tests</t>
+          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
@@ -2914,12 +2922,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>End-to-end demo rehearsal (full run-through, timed)</t>
+          <t>Route inbound messages into the existing RAG assistant</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -2930,7 +2938,7 @@
       <c r="E72" s="16" t="inlineStr"/>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>Schedule before presentation day</t>
+          <t>Can reuse services/rag.js — answerQuestion()</t>
         </is>
       </c>
     </row>
@@ -2940,12 +2948,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Cross-browser / device check (Expo web export)</t>
+          <t>Outbound reply via WhatsApp Cloud API</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
@@ -2962,21 +2970,25 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>README (quick start, architecture, deploy steps)</t>
+          <t>Production Meta Business verification</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr"/>
-      <c r="F74" s="17" t="inlineStr"/>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="13" t="n">
@@ -2984,12 +2996,12 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>ROADMAP.md (phased build plan)</t>
+          <t>Render Blueprint configuration</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
@@ -2998,7 +3010,11 @@
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr"/>
-      <c r="F75" s="17" t="inlineStr"/>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>render.yaml — backend web service + frontend static site</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="13" t="n">
@@ -3006,21 +3022,25 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
+          <t>Backend deployed &amp; health-checked on Render</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr"/>
-      <c r="F76" s="17" t="inlineStr"/>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>Confirm live and reachable before demo day (/health)</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="13" t="n">
@@ -3028,23 +3048,23 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Development task tracker (this file)</t>
+          <t>Frontend deployed as Render static site</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
+          <t>Confirm Expo web export + rewrite rule are working</t>
         </is>
       </c>
     </row>
@@ -3054,23 +3074,23 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
+          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr"/>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
+          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3100,12 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
+          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
@@ -3096,7 +3116,7 @@
       <c r="E79" s="16" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
+          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3126,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
+          <t>Manual acceptance test question bank</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
@@ -3122,7 +3142,7 @@
       <c r="E80" s="16" t="inlineStr"/>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
+          <t>23 questions across consumer + small-business scenarios</t>
         </is>
       </c>
     </row>
@@ -3132,25 +3152,21 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Document supersede/audit-trail model (current vs. superseded)</t>
+          <t>Automated unit/integration tests</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr"/>
-      <c r="F81" s="17" t="inlineStr">
-        <is>
-          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
-        </is>
-      </c>
+      <c r="F81" s="17" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="13" t="n">
@@ -3158,23 +3174,23 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
+          <t>End-to-end demo rehearsal (full run-through, timed)</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr"/>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
+          <t>Schedule before presentation day</t>
         </is>
       </c>
     </row>
@@ -3184,25 +3200,21 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
+          <t>Cross-browser / device check (Expo web export)</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr"/>
-      <c r="F83" s="17" t="inlineStr">
-        <is>
-          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
-        </is>
-      </c>
+      <c r="F83" s="17" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="13" t="n">
@@ -3210,12 +3222,12 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>RAG assistant reflects only current, unresolved exceptions</t>
+          <t>README (quick start, architecture, deploy steps)</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
@@ -3224,11 +3236,7 @@
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr"/>
-      <c r="F84" s="17" t="inlineStr">
-        <is>
-          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
-        </is>
-      </c>
+      <c r="F84" s="17" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="13" t="n">
@@ -3236,25 +3244,21 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>In-browser instant document classification &amp; quality check at upload</t>
+          <t>ROADMAP.md (phased build plan)</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr"/>
-      <c r="F85" s="17" t="inlineStr">
-        <is>
-          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
-        </is>
-      </c>
+      <c r="F85" s="17" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="13" t="n">
@@ -3262,25 +3266,21 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Pre-submission completeness check (required schedules/pages present)</t>
+          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E86" s="16" t="inlineStr"/>
-      <c r="F86" s="17" t="inlineStr">
-        <is>
-          <t>Per document type</t>
-        </is>
-      </c>
+      <c r="F86" s="17" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="13" t="n">
@@ -3288,23 +3288,23 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Blur / glare / legibility detection before accepting an upload</t>
+          <t>Development task tracker (this file)</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr"/>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>Complements existing confidence-score routing in verification.js</t>
+          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
         </is>
       </c>
     </row>
@@ -3319,18 +3319,18 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr"/>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
         </is>
       </c>
     </row>
@@ -3340,23 +3340,23 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr"/>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
         </is>
       </c>
     </row>
@@ -3366,23 +3366,23 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr"/>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
         </is>
       </c>
     </row>
@@ -3392,23 +3392,23 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Shared visibility for all parties on one application</t>
+          <t>Document supersede/audit-trail model (current vs. superseded)</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr"/>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
         </is>
       </c>
     </row>
@@ -3418,23 +3418,23 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr"/>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
         </is>
       </c>
     </row>
@@ -3444,23 +3444,23 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr"/>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
         </is>
       </c>
     </row>
@@ -3470,29 +3470,289 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Self-service grace period / split-payment offers</t>
+          <t>RAG assistant reflects only current, unresolved exceptions</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E94" s="16" t="inlineStr"/>
       <c r="F94" s="17" t="inlineStr">
         <is>
+          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>In-browser instant document classification &amp; quality check at upload</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="inlineStr"/>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Pre-submission completeness check (required schedules/pages present)</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr"/>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>Per document type</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Blur / glare / legibility detection before accepting an upload</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="inlineStr"/>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>Complements existing confidence-score routing in verification.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr"/>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr"/>
+      <c r="F99" s="17" t="inlineStr">
+        <is>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr"/>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Shared visibility for all parties on one application</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr"/>
+      <c r="F101" s="17" t="inlineStr">
+        <is>
+          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr"/>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr"/>
+      <c r="F103" s="17" t="inlineStr">
+        <is>
+          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Self-service grace period / split-payment offers</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="inlineStr"/>
+      <c r="F104" s="17" t="inlineStr">
+        <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F94"/>
-  <conditionalFormatting sqref="D2:D94">
+  <autoFilter ref="A1:F104"/>
+  <conditionalFormatting sqref="D2:D104">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -3504,7 +3764,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3518,7 +3778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4092,9 +4352,149 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Self-registration</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Create a new test account (borrower and officer)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>From the login screen, tap 'Create a test account', fill in name/email/password, pick a role, submit.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Account is created and you're auto-logged-in (no separate login step needed) as that role.</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Lets teammates create their own test users on demand instead of being limited to the 3 seeded logins — directly requested so colleagues could try the app themselves.</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Self-registration</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Duplicate email is rejected</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Try to register with an email that already exists (e.g. officer@loanlens.demo).</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>409 error, clear message — no silent overwrite or duplicate account.</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Basic data integrity check now that account creation isn't limited to a controlled seed script.</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Apply for a loan</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Borrower applies for a new loan end-to-end</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Log in as a borrower (new or existing), tap 'New application', pick a product type, fill in the form, submit.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>A new Application is created with the correct requiredDocTypes for that product; you land directly on its Documents tab with the right items already listed as outstanding.</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>This is the actual 'borrower dashboard' / real loan-application-site experience — previously every application was pre-seeded server-side with no way for a real user to create one themselves.</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Apply for a loan</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Officers don't see the 'New application' option</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Log in as officer@loanlens.demo and look at the Applications list top bar.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>No 'New application' button — only borrowers see it.</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Officers review/manage applications; they don't file one for themselves in this model (distinct from officers being able to upload documents on an applicant's behalf, which is a separate, intentional allowance).</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
-  <conditionalFormatting sqref="G2:G16">
+  <autoFilter ref="A1:G20"/>
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>LEFT($G2,3)="Yes"</formula>
     </cfRule>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2697,18 +2697,18 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Multi-step wizard for the Apply form (Select Product -&gt; Your Info -&gt; Disclosures &amp; Submit)</t>
+          <t>Multi-step wizard for the Apply form (Select Product -&gt; Tell Us About Yourself -&gt; Tell Us More About Yourself -&gt; Disclosures &amp; Submit)</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr"/>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>Currently one scrollable form. Real DAO intake flows are multi-step wizards with these exact section boundaries per Rovo research — a good polish pass, not done yet</t>
+          <t>Matches the real DAO intake step boundaries from Rovo research; per-step validation blocks advancing with missing required fields, progress dots show position</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4492,9 +4492,114 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Apply for a loan</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Wizard step validation blocks incomplete steps</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>On 'Tell Us About Yourself' or 'Tell Us More About Yourself', leave a required field blank and tap Continue.</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>An inline error names what's missing; you stay on the same step — the wizard never lets you reach Disclosures &amp; Submit with incomplete data.</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Prevents a 400 from the server being the first time someone learns a field was missing, several steps later — catches it at the point of entry instead.</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Apply for a loan</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Under-18 date of birth is rejected</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Enter a date of birth less than 18 years before today and submit.</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>400 error: 'Applicants must be 18 or older' — matches the eligibility text already published in every product's policy doc.</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Closes a real gap: every policy already claimed this requirement, but nothing enforced it since there was no DOB field before this session.</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Apply for a loan</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Submission is blocked without consent</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Reach the final step without checking the disclosures/consent box.</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Submit button is disabled (client-side); a direct API call without consentAccepted also gets a 400 server-side.</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Matches the real 'Disclosures &amp; Submit' gate found in every DAO intake flow Rovo surfaced — belt-and-suspenders (UI + server) so it can't be bypassed by skipping the UI.</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
-  <conditionalFormatting sqref="G2:G20">
+  <autoFilter ref="A1:G23"/>
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>LEFT($G2,3)="Yes"</formula>
     </cfRule>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -700,15 +700,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -757,15 +757,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A18,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A18,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A18,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A18,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A18,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A18,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -780,15 +780,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A19,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A19,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A19,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A19,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A19,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A19,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -803,15 +803,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A20,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A20,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A20,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A20,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A20,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A20,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -826,15 +826,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A21,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A21,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A21,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A21,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A21,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A21,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -849,15 +849,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A22,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A22,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A22,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A22,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A22,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A22,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -872,15 +872,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A23,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A23,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A23,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A23,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A23,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A23,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -895,15 +895,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A24,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A24,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A24,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A24,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A24,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A24,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -918,15 +918,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A25,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A25,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A25,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A25,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A25,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A25,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -941,15 +941,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A26,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A26,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A26,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A26,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A26,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A26,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -964,15 +964,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A27,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A27,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A27,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A27,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A27,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A27,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -987,15 +987,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A28,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A28,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A28,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A28,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A28,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A28,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1010,15 +1010,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A29,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A29,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A29,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A29,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A29,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A29,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A30,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A30,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A30,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A30,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A30,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A30,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1056,15 +1056,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A31,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A31,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A31,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A31,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A31,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A31,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1079,15 +1079,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A32,Tasks!$D$2:$D$104,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A32,Tasks!$D$2:$D$105,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A32,Tasks!$D$2:$D$104,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A32,Tasks!$D$2:$D$105,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$104,$A32,Tasks!$D$2:$D$104,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$105,$A32,Tasks!$D$2:$D$105,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1109,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Deterministic rule engine (not LLM — explainable/auditable)</t>
+          <t>MOCK_AI bypass — canned extraction results, no Anthropic API call</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -1924,7 +1924,7 @@
       <c r="E31" s="16" t="inlineStr"/>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>services/verification.js</t>
+          <t>services/mockFixtures.js + extraction.js/rag.js. Added when ANTHROPIC_API_KEY hit a zero credit-balance error blocking all testing — lets verification/live-exception/status-transition testing continue independent of API billing state. Off by default; must not be left on for the real demo</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Name match check</t>
+          <t>Deterministic rule engine (not LLM — explainable/auditable)</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -1948,7 +1948,11 @@
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr"/>
-      <c r="F32" s="17" t="inlineStr"/>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>services/verification.js</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="13" t="n">
@@ -1961,7 +1965,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Income match check (5% tolerance)</t>
+          <t>Name match check</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
@@ -1983,7 +1987,7 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Employer match check</t>
+          <t>Income match check (5% tolerance)</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -2005,7 +2009,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>SSN (last 4) match check</t>
+          <t>Employer match check</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -2027,7 +2031,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Business name / DBA match check</t>
+          <t>SSN (last 4) match check</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
@@ -2036,11 +2040,7 @@
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr"/>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>Demonstrates the entity-name-mismatch pattern found in production loan-servicing tickets</t>
-        </is>
-      </c>
+      <c r="F36" s="17" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="13" t="n">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Annual business revenue match check</t>
+          <t>Business name / DBA match check</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -2062,7 +2062,11 @@
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr"/>
-      <c r="F37" s="17" t="inlineStr"/>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>Demonstrates the entity-name-mismatch pattern found in production loan-servicing tickets</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -2075,7 +2079,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Missing-document detection</t>
+          <t>Annual business revenue match check</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -2084,11 +2088,7 @@
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr"/>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>missingDocuments() in verification.js</t>
-        </is>
-      </c>
+      <c r="F38" s="17" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="13" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Requested-amount affordability check (auto-loan, personal-loan, small-business-loan)</t>
+          <t>Missing-document detection</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -2112,7 +2112,7 @@
       <c r="E39" s="16" t="inlineStr"/>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>New — compares requestedAmount against a simplified income/revenue-based estimate; flags as Warning, never auto-declines. Not a real credit/DSCR calculation</t>
+          <t>missingDocuments() in verification.js</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Warning-level flags surface at the application list level, not just inside document detail</t>
+          <t>Requested-amount affordability check (auto-loan, personal-loan, small-business-loan)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -2138,7 +2138,7 @@
       <c r="E40" s="16" t="inlineStr"/>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>Fixed today — routes/documents.js previously only bumped application status to Needs Review on a hard Mismatch, so an affordability warning was invisible in the officer's list view</t>
+          <t>New — compares requestedAmount against a simplified income/revenue-based estimate; flags as Warning, never auto-declines. Not a real credit/DSCR calculation</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>US currency formatting fixed regardless of server/browser locale</t>
+          <t>Warning-level flags surface at the application list level, not just inside document detail</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -2164,7 +2164,7 @@
       <c r="E41" s="16" t="inlineStr"/>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>toLocaleString() was rendering $3,40,000-style grouping on non-US locales; forced to 'en-US' across backend and frontend</t>
+          <t>Fixed today — routes/documents.js previously only bumped application status to Needs Review on a hard Mismatch, so an affordability warning was invisible in the officer's list view</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>One-click 'request missing document' email to borrower</t>
+          <t>US currency formatting fixed regardless of server/browser locale</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -2190,7 +2190,7 @@
       <c r="E42" s="16" t="inlineStr"/>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>Superseded by the richer in-app live-exception + targeted self-service re-upload flow — see Section 13. No email/SMS needed; the borrower sees and fixes it directly in the app</t>
+          <t>toLocaleString() was rendering $3,40,000-style grouping on non-US locales; forced to 'en-US' across backend and frontend</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
+          <t>One-click 'request missing document' email to borrower</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -2216,7 +2216,7 @@
       <c r="E43" s="16" t="inlineStr"/>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>services/rag.js</t>
+          <t>Superseded by the richer in-app live-exception + targeted self-service re-upload flow — see Section 13. No email/SMS needed; the borrower sees and fixes it directly in the app</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Citation / source attribution on every answer</t>
+          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -2240,7 +2240,11 @@
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr"/>
-      <c r="F44" s="17" t="inlineStr"/>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>services/rag.js</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="13" t="n">
@@ -2253,7 +2257,7 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Role-aware answers (officer vs. borrower)</t>
+          <t>Citation / source attribution on every answer</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -2275,7 +2279,7 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
+          <t>Role-aware answers (officer vs. borrower)</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -2284,11 +2288,7 @@
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr"/>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>Validated in data/seed/test-questions.md</t>
-        </is>
-      </c>
+      <c r="F46" s="17" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Small-business loan Q&amp;A coverage</t>
+          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -2312,7 +2312,7 @@
       <c r="E47" s="16" t="inlineStr"/>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>test-questions.md items 19-23</t>
+          <t>Validated in data/seed/test-questions.md</t>
         </is>
       </c>
     </row>
@@ -2327,18 +2327,18 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>WhatsApp channel for the assistant</t>
+          <t>Small-business loan Q&amp;A coverage</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr"/>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>See Section 9</t>
+          <t>test-questions.md items 19-23</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
+          <t>WhatsApp channel for the assistant</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
@@ -2364,7 +2364,7 @@
       <c r="E49" s="16" t="inlineStr"/>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>Recommended add-on from pain-point research — not yet scoped</t>
+          <t>See Section 9</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Embeddings + vector search (scale-up path)</t>
+          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
@@ -2390,7 +2390,7 @@
       <c r="E50" s="16" t="inlineStr"/>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
+          <t>Recommended add-on from pain-point research — not yet scoped</t>
         </is>
       </c>
     </row>
@@ -2400,23 +2400,23 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Navigation shell (auth-gated stack navigation)</t>
+          <t>Embeddings + vector search (scale-up path)</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr"/>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>App.js</t>
+          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Login screen</t>
+          <t>Navigation shell (auth-gated stack navigation)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
@@ -2440,7 +2440,11 @@
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr"/>
-      <c r="F52" s="17" t="inlineStr"/>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>App.js</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -2453,7 +2457,7 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Applications list screen</t>
+          <t>Login screen</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -2462,11 +2466,7 @@
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr"/>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>Officer sees all; borrower sees only their own</t>
-        </is>
-      </c>
+      <c r="F53" s="17" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="13" t="n">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Application detail screen (header facts + tab bar)</t>
+          <t>Applications list screen</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="E54" s="16" t="inlineStr"/>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Branches fact display by product type</t>
+          <t>Officer sees all; borrower sees only their own</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Documents tab — upload + extracted fields display</t>
+          <t>Application detail screen (header facts + tab bar)</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -2514,7 +2514,11 @@
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr"/>
-      <c r="F55" s="17" t="inlineStr"/>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>Branches fact display by product type</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="13" t="n">
@@ -2527,7 +2531,7 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Verification tab — checks + missing documents</t>
+          <t>Documents tab — upload + extracted fields display</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -2549,7 +2553,7 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Assistant tab — chat UI with source chips</t>
+          <t>Verification tab — checks + missing documents</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -2571,7 +2575,7 @@
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Small-business-specific detail view (business name / revenue facts)</t>
+          <t>Assistant tab — chat UI with source chips</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
@@ -2593,7 +2597,7 @@
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>Fintech-styled visual design pass</t>
+          <t>Small-business-specific detail view (business name / revenue facts)</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -2602,11 +2606,7 @@
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr"/>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>Per recent commit history</t>
-        </is>
-      </c>
+      <c r="F59" s="17" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="13" t="n">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Sign-up screen (self-registration, role picker)</t>
+          <t>Fintech-styled visual design pass</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
@@ -2630,7 +2630,7 @@
       <c r="E60" s="16" t="inlineStr"/>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>SignUpScreen.js</t>
+          <t>Per recent commit history</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>New Application screen ('Apply for a Loan')</t>
+          <t>Sign-up screen (self-registration, role picker)</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
@@ -2656,7 +2656,7 @@
       <c r="E61" s="16" t="inlineStr"/>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>NewApplicationScreen.js — product-type picker with conditional fields (consumer income/employer vs. business name/revenue), submits to POST /applications then lands on that application's Documents tab</t>
+          <t>SignUpScreen.js</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>'New application' entry point on the borrower's Applications list</t>
+          <t>New Application screen ('Apply for a Loan')</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
@@ -2682,7 +2682,7 @@
       <c r="E62" s="16" t="inlineStr"/>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>Officer role doesn't see this button — they don't file applications for themselves</t>
+          <t>NewApplicationScreen.js — product-type picker with conditional fields (consumer income/employer vs. business name/revenue), submits to POST /applications then lands on that application's Documents tab</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Multi-step wizard for the Apply form (Select Product -&gt; Tell Us About Yourself -&gt; Tell Us More About Yourself -&gt; Disclosures &amp; Submit)</t>
+          <t>'New application' entry point on the borrower's Applications list</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
@@ -2708,7 +2708,7 @@
       <c r="E63" s="16" t="inlineStr"/>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>Matches the real DAO intake step boundaries from Rovo research; per-step validation blocks advancing with missing required fields, progress dots show position</t>
+          <t>Officer role doesn't see this button — they don't file applications for themselves</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus — 6 markdown policies</t>
+          <t>Multi-step wizard for the Apply form (Select Product -&gt; Tell Us About Yourself -&gt; Tell Us More About Yourself -&gt; Disclosures &amp; Submit)</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="E64" s="16" t="inlineStr"/>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
+          <t>Matches the real DAO intake step boundaries from Rovo research; per-step validation blocks advancing with missing required fields, progress dots show position</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Small Business Loan Requirements policy</t>
+          <t>Policy corpus — 6 markdown policies</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
@@ -2760,7 +2760,7 @@
       <c r="E65" s="16" t="inlineStr"/>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>data/policies/small-business-loan-requirements.md</t>
+          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
+          <t>Small Business Loan Requirements policy</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -2786,7 +2786,7 @@
       <c r="E66" s="16" t="inlineStr"/>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
+          <t>data/policies/small-business-loan-requirements.md</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
+          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
@@ -2812,7 +2812,7 @@
       <c r="E67" s="16" t="inlineStr"/>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
+          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Test question bank (acceptance checklist)</t>
+          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
@@ -2838,7 +2838,7 @@
       <c r="E68" s="16" t="inlineStr"/>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
+          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Demo script</t>
+          <t>Test question bank (acceptance checklist)</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
@@ -2864,7 +2864,7 @@
       <c r="E69" s="16" t="inlineStr"/>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
+          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
         </is>
       </c>
     </row>
@@ -2874,23 +2874,23 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Meta developer app + free sandbox test number</t>
+          <t>Demo script</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E70" s="16" t="inlineStr"/>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>Self-serve, free, no leadership approval needed for the demo</t>
+          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
+          <t>Meta developer app + free sandbox test number</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
@@ -2914,7 +2914,11 @@
         </is>
       </c>
       <c r="E71" s="16" t="inlineStr"/>
-      <c r="F71" s="17" t="inlineStr"/>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>Self-serve, free, no leadership approval needed for the demo</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="13" t="n">
@@ -2927,7 +2931,7 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Route inbound messages into the existing RAG assistant</t>
+          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -2936,11 +2940,7 @@
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr"/>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>Can reuse services/rag.js — answerQuestion()</t>
-        </is>
-      </c>
+      <c r="F72" s="17" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="13" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Outbound reply via WhatsApp Cloud API</t>
+          <t>Route inbound messages into the existing RAG assistant</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
@@ -2962,7 +2962,11 @@
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr"/>
-      <c r="F73" s="17" t="inlineStr"/>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>Can reuse services/rag.js — answerQuestion()</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="13" t="n">
@@ -2975,7 +2979,7 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Production Meta Business verification</t>
+          <t>Outbound reply via WhatsApp Cloud API</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -2984,11 +2988,7 @@
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr"/>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
-        </is>
-      </c>
+      <c r="F74" s="17" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="13" t="n">
@@ -2996,23 +2996,23 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Render Blueprint configuration</t>
+          <t>Production Meta Business verification</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr"/>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>render.yaml — backend web service + frontend static site</t>
+          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
         </is>
       </c>
     </row>
@@ -3027,18 +3027,18 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Backend deployed &amp; health-checked on Render</t>
+          <t>Render Blueprint configuration</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr"/>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>Confirm live and reachable before demo day (/health)</t>
+          <t>render.yaml — backend web service + frontend static site</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Frontend deployed as Render static site</t>
+          <t>Backend deployed &amp; health-checked on Render</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
@@ -3064,7 +3064,7 @@
       <c r="E77" s="16" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>Confirm Expo web export + rewrite rule are working</t>
+          <t>Confirm live and reachable before demo day (/health)</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
+          <t>Frontend deployed as Render static site</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -3090,7 +3090,7 @@
       <c r="E78" s="16" t="inlineStr"/>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
+          <t>Confirm Expo web export + rewrite rule are working</t>
         </is>
       </c>
     </row>
@@ -3105,18 +3105,18 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
+          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Manual acceptance test question bank</t>
+          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
@@ -3142,7 +3142,7 @@
       <c r="E80" s="16" t="inlineStr"/>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>23 questions across consumer + small-business scenarios</t>
+          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
         </is>
       </c>
     </row>
@@ -3157,16 +3157,20 @@
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Automated unit/integration tests</t>
+          <t>Manual acceptance test question bank</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr"/>
-      <c r="F81" s="17" t="inlineStr"/>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>23 questions across consumer + small-business scenarios</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="13" t="n">
@@ -3179,7 +3183,7 @@
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>End-to-end demo rehearsal (full run-through, timed)</t>
+          <t>Automated unit/integration tests</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
@@ -3188,11 +3192,7 @@
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr"/>
-      <c r="F82" s="17" t="inlineStr">
-        <is>
-          <t>Schedule before presentation day</t>
-        </is>
-      </c>
+      <c r="F82" s="17" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="13" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Cross-browser / device check (Expo web export)</t>
+          <t>End-to-end demo rehearsal (full run-through, timed)</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
@@ -3214,7 +3214,11 @@
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr"/>
-      <c r="F83" s="17" t="inlineStr"/>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>Schedule before presentation day</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="13" t="n">
@@ -3222,17 +3226,17 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>README (quick start, architecture, deploy steps)</t>
+          <t>Cross-browser / device check (Expo web export)</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr"/>
@@ -3249,7 +3253,7 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>ROADMAP.md (phased build plan)</t>
+          <t>README (quick start, architecture, deploy steps)</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
@@ -3271,7 +3275,7 @@
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
+          <t>ROADMAP.md (phased build plan)</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
@@ -3293,7 +3297,7 @@
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Development task tracker (this file)</t>
+          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
@@ -3302,11 +3306,7 @@
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr"/>
-      <c r="F87" s="17" t="inlineStr">
-        <is>
-          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
-        </is>
-      </c>
+      <c r="F87" s="17" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="13" t="n">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
+          <t>Development task tracker (this file)</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
@@ -3330,7 +3330,7 @@
       <c r="E88" s="16" t="inlineStr"/>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
+          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
+          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
@@ -3356,7 +3356,7 @@
       <c r="E89" s="16" t="inlineStr"/>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
+          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
+          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
@@ -3382,7 +3382,7 @@
       <c r="E90" s="16" t="inlineStr"/>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
+          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Document supersede/audit-trail model (current vs. superseded)</t>
+          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
@@ -3408,7 +3408,7 @@
       <c r="E91" s="16" t="inlineStr"/>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
+          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
+          <t>Document supersede/audit-trail model (current vs. superseded)</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr">
@@ -3434,7 +3434,7 @@
       <c r="E92" s="16" t="inlineStr"/>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
+          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
+          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
@@ -3460,7 +3460,7 @@
       <c r="E93" s="16" t="inlineStr"/>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
+          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>RAG assistant reflects only current, unresolved exceptions</t>
+          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
@@ -3486,7 +3486,7 @@
       <c r="E94" s="16" t="inlineStr"/>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
+          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
         </is>
       </c>
     </row>
@@ -3501,18 +3501,18 @@
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>In-browser instant document classification &amp; quality check at upload</t>
+          <t>RAG assistant reflects only current, unresolved exceptions</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr"/>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
+          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Pre-submission completeness check (required schedules/pages present)</t>
+          <t>In-browser instant document classification &amp; quality check at upload</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
@@ -3538,7 +3538,7 @@
       <c r="E96" s="16" t="inlineStr"/>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>Per document type</t>
+          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Blur / glare / legibility detection before accepting an upload</t>
+          <t>Pre-submission completeness check (required schedules/pages present)</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
@@ -3564,7 +3564,7 @@
       <c r="E97" s="16" t="inlineStr"/>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>Complements existing confidence-score routing in verification.js</t>
+          <t>Per document type</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+          <t>Blur / glare / legibility detection before accepting an upload</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
@@ -3590,7 +3590,7 @@
       <c r="E98" s="16" t="inlineStr"/>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+          <t>Complements existing confidence-score routing in verification.js</t>
         </is>
       </c>
     </row>
@@ -3600,12 +3600,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+          <t>Auto pre-fill of underwriting review fields from extracted data</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       <c r="E99" s="16" t="inlineStr"/>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
@@ -3642,7 +3642,7 @@
       <c r="E100" s="16" t="inlineStr"/>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Shared visibility for all parties on one application</t>
+          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -3668,7 +3668,7 @@
       <c r="E101" s="16" t="inlineStr"/>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+          <t>Shared visibility for all parties on one application</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -3694,7 +3694,7 @@
       <c r="E102" s="16" t="inlineStr"/>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
@@ -3720,7 +3720,7 @@
       <c r="E103" s="16" t="inlineStr"/>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Self-service grace period / split-payment offers</t>
+          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
@@ -3746,13 +3746,39 @@
       <c r="E104" s="16" t="inlineStr"/>
       <c r="F104" s="17" t="inlineStr">
         <is>
+          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>Self-service grace period / split-payment offers</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr"/>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F104"/>
-  <conditionalFormatting sqref="D2:D104">
+  <autoFilter ref="A1:F105"/>
+  <conditionalFormatting sqref="D2:D105">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -3764,7 +3790,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3778,7 +3804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4597,9 +4623,79 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>MOCK_AI bypass</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Mock extraction reproduces the exact planted mismatch for a known seed filename</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Set MOCK_AI=true, upload jordan-rivera-pay-stub.png.</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Extraction returns income $4,200 (no real API call); verification flags the same $5,000 vs $4,200 mismatch as the real Claude call would.</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Confirms the bypass is faithful to real behavior, not just a stub that unblocks the UI — ran this exact case directly against verification.js and got the identical flagged result.</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>MOCK_AI bypass</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Unrecognized filename in mock mode degrades gracefully</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>With MOCK_AI=true, upload any file not in the known seed set.</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Returns docType 'unknown', confidence 0.3 — routes to human review, same as a real illegible document, instead of throwing.</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>So testing with an arbitrary file doesn't crash the upload flow while mock mode is on.</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>Yes — executed directly against verification.js with real inputs (see chat transcript)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
-  <conditionalFormatting sqref="G2:G23">
+  <autoFilter ref="A1:G25"/>
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>LEFT($G2,3)="Yes"</formula>
     </cfRule>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -700,15 +700,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -757,15 +757,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A18,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A18,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A18,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A18,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A18,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A18,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -780,15 +780,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A19,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A19,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A19,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A19,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A19,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A19,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -803,15 +803,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A20,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A20,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A20,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A20,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A20,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A20,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -826,15 +826,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A21,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A21,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A21,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A21,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A21,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A21,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -849,15 +849,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A22,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A22,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A22,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A22,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A22,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A22,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -872,15 +872,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A23,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A23,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A23,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A23,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A23,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A23,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -895,15 +895,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A24,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A24,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A24,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A24,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A24,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A24,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -918,15 +918,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A25,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A25,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A25,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A25,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A25,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A25,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -941,15 +941,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A26,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A26,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A26,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A26,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A26,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A26,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -964,15 +964,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A27,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A27,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A27,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A27,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A27,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A27,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -987,15 +987,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A28,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A28,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A28,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A28,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A28,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A28,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1010,15 +1010,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A29,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A29,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A29,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A29,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A29,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A29,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A30,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A30,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A30,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A30,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A30,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A30,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1056,15 +1056,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A31,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A31,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A31,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A31,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A31,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A31,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1079,15 +1079,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A32,Tasks!$D$2:$D$105,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A32,Tasks!$D$2:$D$106,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A32,Tasks!$D$2:$D$105,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A32,Tasks!$D$2:$D$106,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$105,$A32,Tasks!$D$2:$D$105,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$106,$A32,Tasks!$D$2:$D$106,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1109,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2900,23 +2900,23 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Meta developer app + free sandbox test number</t>
+          <t>Indian-named seed borrowers with real logins (Priya Nair, Arjun Mehta)</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E71" s="16" t="inlineStr"/>
       <c r="F71" s="17" t="inlineStr">
         <is>
-          <t>Self-serve, free, no leadership approval needed for the demo</t>
+          <t>Priya Nair already existed as an application-only record (no login); Arjun Mehta replaces the former 'Marcus Webb' auto-loan record (safe — that name wasn't referenced in DEMO_SCRIPT.md or test-questions.md). Standing preference going forward: use Indian names for any new seed/test data added</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
+          <t>Meta developer app + free sandbox test number</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -2940,7 +2940,11 @@
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr"/>
-      <c r="F72" s="17" t="inlineStr"/>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>Self-serve, free, no leadership approval needed for the demo</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="13" t="n">
@@ -2953,7 +2957,7 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Route inbound messages into the existing RAG assistant</t>
+          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
@@ -2962,11 +2966,7 @@
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr"/>
-      <c r="F73" s="17" t="inlineStr">
-        <is>
-          <t>Can reuse services/rag.js — answerQuestion()</t>
-        </is>
-      </c>
+      <c r="F73" s="17" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="13" t="n">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Outbound reply via WhatsApp Cloud API</t>
+          <t>Route inbound messages into the existing RAG assistant</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -2988,7 +2988,11 @@
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr"/>
-      <c r="F74" s="17" t="inlineStr"/>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>Can reuse services/rag.js — answerQuestion()</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="13" t="n">
@@ -3001,7 +3005,7 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Production Meta Business verification</t>
+          <t>Outbound reply via WhatsApp Cloud API</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
@@ -3010,11 +3014,7 @@
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr"/>
-      <c r="F75" s="17" t="inlineStr">
-        <is>
-          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
-        </is>
-      </c>
+      <c r="F75" s="17" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="13" t="n">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Render Blueprint configuration</t>
+          <t>Production Meta Business verification</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr"/>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>render.yaml — backend web service + frontend static site</t>
+          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
         </is>
       </c>
     </row>
@@ -3053,18 +3053,18 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Backend deployed &amp; health-checked on Render</t>
+          <t>Render Blueprint configuration</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>Confirm live and reachable before demo day (/health)</t>
+          <t>render.yaml — backend web service + frontend static site</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Frontend deployed as Render static site</t>
+          <t>Backend deployed &amp; health-checked on Render</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -3090,7 +3090,7 @@
       <c r="E78" s="16" t="inlineStr"/>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>Confirm Expo web export + rewrite rule are working</t>
+          <t>Confirm live and reachable before demo day (/health)</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
+          <t>Frontend deployed as Render static site</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="E79" s="16" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
+          <t>Confirm Expo web export + rewrite rule are working</t>
         </is>
       </c>
     </row>
@@ -3131,18 +3131,18 @@
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
+          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr"/>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Manual acceptance test question bank</t>
+          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
@@ -3168,7 +3168,7 @@
       <c r="E81" s="16" t="inlineStr"/>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>23 questions across consumer + small-business scenarios</t>
+          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
         </is>
       </c>
     </row>
@@ -3183,16 +3183,20 @@
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Automated unit/integration tests</t>
+          <t>Manual acceptance test question bank</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr"/>
-      <c r="F82" s="17" t="inlineStr"/>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>23 questions across consumer + small-business scenarios</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="13" t="n">
@@ -3205,7 +3209,7 @@
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>End-to-end demo rehearsal (full run-through, timed)</t>
+          <t>Automated unit/integration tests</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
@@ -3214,11 +3218,7 @@
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr"/>
-      <c r="F83" s="17" t="inlineStr">
-        <is>
-          <t>Schedule before presentation day</t>
-        </is>
-      </c>
+      <c r="F83" s="17" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="13" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Cross-browser / device check (Expo web export)</t>
+          <t>End-to-end demo rehearsal (full run-through, timed)</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
@@ -3240,7 +3240,11 @@
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr"/>
-      <c r="F84" s="17" t="inlineStr"/>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>Schedule before presentation day</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="13" t="n">
@@ -3248,17 +3252,17 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>README (quick start, architecture, deploy steps)</t>
+          <t>Cross-browser / device check (Expo web export)</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr"/>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>ROADMAP.md (phased build plan)</t>
+          <t>README (quick start, architecture, deploy steps)</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
@@ -3297,7 +3301,7 @@
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
+          <t>ROADMAP.md (phased build plan)</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
@@ -3319,7 +3323,7 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Development task tracker (this file)</t>
+          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
@@ -3328,11 +3332,7 @@
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr"/>
-      <c r="F88" s="17" t="inlineStr">
-        <is>
-          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
-        </is>
-      </c>
+      <c r="F88" s="17" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="13" t="n">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
+          <t>Development task tracker (this file)</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
@@ -3356,7 +3356,7 @@
       <c r="E89" s="16" t="inlineStr"/>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
+          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
+          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
@@ -3382,7 +3382,7 @@
       <c r="E90" s="16" t="inlineStr"/>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
+          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
+          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
@@ -3408,7 +3408,7 @@
       <c r="E91" s="16" t="inlineStr"/>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
+          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Document supersede/audit-trail model (current vs. superseded)</t>
+          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr">
@@ -3434,7 +3434,7 @@
       <c r="E92" s="16" t="inlineStr"/>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
+          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
+          <t>Document supersede/audit-trail model (current vs. superseded)</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
@@ -3460,7 +3460,7 @@
       <c r="E93" s="16" t="inlineStr"/>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
+          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
+          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
@@ -3486,7 +3486,7 @@
       <c r="E94" s="16" t="inlineStr"/>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
+          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>RAG assistant reflects only current, unresolved exceptions</t>
+          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
@@ -3512,7 +3512,7 @@
       <c r="E95" s="16" t="inlineStr"/>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
+          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
         </is>
       </c>
     </row>
@@ -3527,18 +3527,18 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>In-browser instant document classification &amp; quality check at upload</t>
+          <t>RAG assistant reflects only current, unresolved exceptions</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E96" s="16" t="inlineStr"/>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
+          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Pre-submission completeness check (required schedules/pages present)</t>
+          <t>In-browser instant document classification &amp; quality check at upload</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
@@ -3564,7 +3564,7 @@
       <c r="E97" s="16" t="inlineStr"/>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>Per document type</t>
+          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Blur / glare / legibility detection before accepting an upload</t>
+          <t>Pre-submission completeness check (required schedules/pages present)</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
@@ -3590,7 +3590,7 @@
       <c r="E98" s="16" t="inlineStr"/>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>Complements existing confidence-score routing in verification.js</t>
+          <t>Per document type</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+          <t>Blur / glare / legibility detection before accepting an upload</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       <c r="E99" s="16" t="inlineStr"/>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+          <t>Complements existing confidence-score routing in verification.js</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+          <t>Auto pre-fill of underwriting review fields from extracted data</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
@@ -3642,7 +3642,7 @@
       <c r="E100" s="16" t="inlineStr"/>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -3668,7 +3668,7 @@
       <c r="E101" s="16" t="inlineStr"/>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Shared visibility for all parties on one application</t>
+          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -3694,7 +3694,7 @@
       <c r="E102" s="16" t="inlineStr"/>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+          <t>Shared visibility for all parties on one application</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
@@ -3720,7 +3720,7 @@
       <c r="E103" s="16" t="inlineStr"/>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
@@ -3746,7 +3746,7 @@
       <c r="E104" s="16" t="inlineStr"/>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Self-service grace period / split-payment offers</t>
+          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
@@ -3772,13 +3772,39 @@
       <c r="E105" s="16" t="inlineStr"/>
       <c r="F105" s="17" t="inlineStr">
         <is>
+          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Self-service grace period / split-payment offers</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr"/>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F105"/>
-  <conditionalFormatting sqref="D2:D105">
+  <autoFilter ref="A1:F106"/>
+  <conditionalFormatting sqref="D2:D106">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -3790,7 +3816,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -700,15 +700,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -757,15 +757,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A18,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A18,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A18,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A18,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A18,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A18,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -780,15 +780,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A19,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A19,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A19,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A19,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A19,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A19,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -803,15 +803,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A20,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A20,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A20,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A20,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A20,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A20,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -826,15 +826,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A21,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A21,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A21,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A21,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A21,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A21,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -849,15 +849,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A22,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A22,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A22,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A22,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A22,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A22,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -872,15 +872,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A23,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A23,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A23,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A23,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A23,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A23,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -895,15 +895,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A24,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A24,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A24,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A24,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A24,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A24,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -918,15 +918,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A25,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A25,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A25,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A25,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A25,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A25,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -941,15 +941,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A26,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A26,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A26,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A26,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A26,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A26,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -964,15 +964,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A27,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A27,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A27,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A27,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A27,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A27,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -987,15 +987,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A28,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A28,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A28,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A28,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A28,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A28,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1010,15 +1010,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A29,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A29,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A29,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A29,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A29,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A29,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A30,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A30,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A30,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A30,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A30,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A30,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1056,15 +1056,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A31,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A31,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A31,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A31,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A31,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A31,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1079,15 +1079,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A32,Tasks!$D$2:$D$106,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A32,Tasks!$D$2:$D$111,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A32,Tasks!$D$2:$D$106,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A32,Tasks!$D$2:$D$111,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$106,$A32,Tasks!$D$2:$D$106,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$111,$A32,Tasks!$D$2:$D$111,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1109,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus — 6 markdown policies</t>
+          <t>Persistent branded header on every authenticated screen (logo, page title, profile menu)</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
@@ -2760,7 +2760,7 @@
       <c r="E65" s="16" t="inlineStr"/>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
+          <t>components/BrandHeader.js, wired globally via Stack.Navigator screenOptions.header — previously each screen had its own inconsistent title ('Application', 'Apply for a Loan') with no logo/branding and no way to sign out except from the Applications list</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Small Business Loan Requirements policy</t>
+          <t>Responsive left sidebar navigation (desktop-width viewports)</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -2786,7 +2786,7 @@
       <c r="E66" s="16" t="inlineStr"/>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>data/policies/small-business-loan-requirements.md</t>
+          <t>components/Sidebar.js — Applications / Apply for a Loan links, role-aware. Rendered outside the Stack.Navigator's own subtree so it persists across screen changes; navigates via a navigationRef (React Navigation's documented pattern for navigating from outside the navigator tree, since useNavigation() isn't available there). Hidden below 900px width — mobile/narrow-browser experience unchanged</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
+          <t>Floating Assistant button on the application detail screen</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
@@ -2812,7 +2812,7 @@
       <c r="E67" s="16" t="inlineStr"/>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
+          <t>Bottom-right chat-bubble FAB jumps straight to the Assistant tab; hidden while already on that tab</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
+          <t>Issue-list rendering split into individual rows (not one run-on paragraph)</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
@@ -2838,7 +2838,7 @@
       <c r="E68" s="16" t="inlineStr"/>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
+          <t>See prior commit — DocumentsTab now renders each flagged check on a document as its own row</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Test question bank (acceptance checklist)</t>
+          <t>Policy corpus — 6 markdown policies</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
@@ -2864,7 +2864,7 @@
       <c r="E69" s="16" t="inlineStr"/>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
+          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Demo script</t>
+          <t>Small Business Loan Requirements policy</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -2890,7 +2890,7 @@
       <c r="E70" s="16" t="inlineStr"/>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
+          <t>data/policies/small-business-loan-requirements.md</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Indian-named seed borrowers with real logins (Priya Nair, Arjun Mehta)</t>
+          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
@@ -2916,7 +2916,7 @@
       <c r="E71" s="16" t="inlineStr"/>
       <c r="F71" s="17" t="inlineStr">
         <is>
-          <t>Priya Nair already existed as an application-only record (no login); Arjun Mehta replaces the former 'Marcus Webb' auto-loan record (safe — that name wasn't referenced in DEMO_SCRIPT.md or test-questions.md). Standing preference going forward: use Indian names for any new seed/test data added</t>
+          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
         </is>
       </c>
     </row>
@@ -2926,23 +2926,23 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Meta developer app + free sandbox test number</t>
+          <t>Breadth/QA demo documents — Priya Nair (clean/happy-path) and Arjun Mehta (employer-mismatch warning)</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr"/>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>Self-serve, free, no leadership approval needed for the demo</t>
+          <t>Priya Nair and Arjun Mehta previously had zero document images despite being seeded applicants. Arjun's set is the only scenario exercising the softer 'warning' tier (employer differs) rather than a hard 'mismatch' — verified both against verification.js directly (Priya: overall 'pass'; Arjun: only the Employer check fires, overall 'needs-review')</t>
         </is>
       </c>
     </row>
@@ -2952,21 +2952,25 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
+          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr"/>
-      <c r="F73" s="17" t="inlineStr"/>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="13" t="n">
@@ -2974,23 +2978,23 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Route inbound messages into the existing RAG assistant</t>
+          <t>Test question bank (acceptance checklist)</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr"/>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>Can reuse services/rag.js — answerQuestion()</t>
+          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
         </is>
       </c>
     </row>
@@ -3000,21 +3004,25 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Outbound reply via WhatsApp Cloud API</t>
+          <t>Demo script</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr"/>
-      <c r="F75" s="17" t="inlineStr"/>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="13" t="n">
@@ -3022,23 +3030,23 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Production Meta Business verification</t>
+          <t>Indian-named seed borrowers with real logins (Priya Nair, Arjun Mehta)</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr"/>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
+          <t>Priya Nair already existed as an application-only record (no login); Arjun Mehta replaces the former 'Marcus Webb' auto-loan record (safe — that name wasn't referenced in DEMO_SCRIPT.md or test-questions.md). Standing preference going forward: use Indian names for any new seed/test data added</t>
         </is>
       </c>
     </row>
@@ -3048,23 +3056,23 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Render Blueprint configuration</t>
+          <t>Meta developer app + free sandbox test number</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>render.yaml — backend web service + frontend static site</t>
+          <t>Self-serve, free, no leadership approval needed for the demo</t>
         </is>
       </c>
     </row>
@@ -3074,25 +3082,21 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Backend deployed &amp; health-checked on Render</t>
+          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr"/>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t>Confirm live and reachable before demo day (/health)</t>
-        </is>
-      </c>
+      <c r="F78" s="17" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="13" t="n">
@@ -3100,23 +3104,23 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Frontend deployed as Render static site</t>
+          <t>Route inbound messages into the existing RAG assistant</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>Confirm Expo web export + rewrite rule are working</t>
+          <t>Can reuse services/rag.js — answerQuestion()</t>
         </is>
       </c>
     </row>
@@ -3126,25 +3130,21 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
+          <t>Outbound reply via WhatsApp Cloud API</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr"/>
-      <c r="F80" s="17" t="inlineStr">
-        <is>
-          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
-        </is>
-      </c>
+      <c r="F80" s="17" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="13" t="n">
@@ -3152,23 +3152,23 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
+          <t>Production Meta Business verification</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr"/>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Manual acceptance test question bank</t>
+          <t>Render Blueprint configuration</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
@@ -3194,7 +3194,7 @@
       <c r="E82" s="16" t="inlineStr"/>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>23 questions across consumer + small-business scenarios</t>
+          <t>render.yaml — backend web service + frontend static site</t>
         </is>
       </c>
     </row>
@@ -3204,21 +3204,25 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Automated unit/integration tests</t>
+          <t>Backend deployed &amp; health-checked on Render</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr"/>
-      <c r="F83" s="17" t="inlineStr"/>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>Confirm live and reachable before demo day (/health)</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="13" t="n">
@@ -3226,23 +3230,23 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>End-to-end demo rehearsal (full run-through, timed)</t>
+          <t>Frontend deployed as Render static site</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr"/>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Schedule before presentation day</t>
+          <t>Confirm Expo web export + rewrite rule are working</t>
         </is>
       </c>
     </row>
@@ -3252,21 +3256,25 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Cross-browser / device check (Expo web export)</t>
+          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr"/>
-      <c r="F85" s="17" t="inlineStr"/>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="13" t="n">
@@ -3274,12 +3282,12 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>README (quick start, architecture, deploy steps)</t>
+          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
@@ -3288,7 +3296,11 @@
         </is>
       </c>
       <c r="E86" s="16" t="inlineStr"/>
-      <c r="F86" s="17" t="inlineStr"/>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="13" t="n">
@@ -3296,12 +3308,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>ROADMAP.md (phased build plan)</t>
+          <t>Manual acceptance test question bank</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
@@ -3310,7 +3322,11 @@
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr"/>
-      <c r="F87" s="17" t="inlineStr"/>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>23 questions across consumer + small-business scenarios</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="13" t="n">
@@ -3318,17 +3334,17 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
+          <t>Automated unit/integration tests</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr"/>
@@ -3340,23 +3356,23 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Development task tracker (this file)</t>
+          <t>End-to-end demo rehearsal (full run-through, timed)</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr"/>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
+          <t>Schedule before presentation day</t>
         </is>
       </c>
     </row>
@@ -3366,25 +3382,21 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
+          <t>Cross-browser / device check (Expo web export)</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr"/>
-      <c r="F90" s="17" t="inlineStr">
-        <is>
-          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
-        </is>
-      </c>
+      <c r="F90" s="17" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="13" t="n">
@@ -3392,12 +3404,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
+          <t>README (quick start, architecture, deploy steps)</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
@@ -3406,11 +3418,7 @@
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr"/>
-      <c r="F91" s="17" t="inlineStr">
-        <is>
-          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
-        </is>
-      </c>
+      <c r="F91" s="17" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="13" t="n">
@@ -3418,12 +3426,12 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
+          <t>ROADMAP.md (phased build plan)</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr">
@@ -3432,11 +3440,7 @@
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr"/>
-      <c r="F92" s="17" t="inlineStr">
-        <is>
-          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
-        </is>
-      </c>
+      <c r="F92" s="17" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="13" t="n">
@@ -3444,12 +3448,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Document supersede/audit-trail model (current vs. superseded)</t>
+          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
@@ -3458,11 +3462,7 @@
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr"/>
-      <c r="F93" s="17" t="inlineStr">
-        <is>
-          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
-        </is>
-      </c>
+      <c r="F93" s="17" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="13" t="n">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
+          <t>Development task tracker (this file)</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
@@ -3486,7 +3486,7 @@
       <c r="E94" s="16" t="inlineStr"/>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
+          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
+          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
@@ -3512,7 +3512,7 @@
       <c r="E95" s="16" t="inlineStr"/>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
+          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>RAG assistant reflects only current, unresolved exceptions</t>
+          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
@@ -3538,7 +3538,7 @@
       <c r="E96" s="16" t="inlineStr"/>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
+          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
         </is>
       </c>
     </row>
@@ -3553,18 +3553,18 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>In-browser instant document classification &amp; quality check at upload</t>
+          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E97" s="16" t="inlineStr"/>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
+          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
         </is>
       </c>
     </row>
@@ -3579,18 +3579,18 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Pre-submission completeness check (required schedules/pages present)</t>
+          <t>Document supersede/audit-trail model (current vs. superseded)</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E98" s="16" t="inlineStr"/>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>Per document type</t>
+          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
         </is>
       </c>
     </row>
@@ -3605,18 +3605,18 @@
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Blur / glare / legibility detection before accepting an upload</t>
+          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr"/>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>Complements existing confidence-score routing in verification.js</t>
+          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
         </is>
       </c>
     </row>
@@ -3631,18 +3631,18 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E100" s="16" t="inlineStr"/>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
         </is>
       </c>
     </row>
@@ -3652,23 +3652,23 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+          <t>RAG assistant reflects only current, unresolved exceptions</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E101" s="16" t="inlineStr"/>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
         </is>
       </c>
     </row>
@@ -3678,12 +3678,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+          <t>In-browser instant document classification &amp; quality check at upload</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -3694,7 +3694,7 @@
       <c r="E102" s="16" t="inlineStr"/>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Shared visibility for all parties on one application</t>
+          <t>Pre-submission completeness check (required schedules/pages present)</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
@@ -3720,7 +3720,7 @@
       <c r="E103" s="16" t="inlineStr"/>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+          <t>Per document type</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+          <t>Blur / glare / legibility detection before accepting an upload</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
@@ -3746,7 +3746,7 @@
       <c r="E104" s="16" t="inlineStr"/>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+          <t>Complements existing confidence-score routing in verification.js</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+          <t>Auto pre-fill of underwriting review fields from extracted data</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
@@ -3772,7 +3772,7 @@
       <c r="E105" s="16" t="inlineStr"/>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Self-service grace period / split-payment offers</t>
+          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
@@ -3798,13 +3798,143 @@
       <c r="E106" s="16" t="inlineStr"/>
       <c r="F106" s="17" t="inlineStr">
         <is>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr"/>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="13" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Shared visibility for all parties on one application</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="inlineStr"/>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="13" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr"/>
+      <c r="F109" s="17" t="inlineStr">
+        <is>
+          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="13" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E110" s="16" t="inlineStr"/>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>Self-service grace period / split-payment offers</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E111" s="16" t="inlineStr"/>
+      <c r="F111" s="17" t="inlineStr">
+        <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F106"/>
-  <conditionalFormatting sqref="D2:D106">
+  <autoFilter ref="A1:F111"/>
+  <conditionalFormatting sqref="D2:D111">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -3816,7 +3946,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -700,15 +700,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -757,15 +757,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A18,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A18,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A18,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A18,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A18,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A18,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -780,15 +780,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A19,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A19,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A19,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A19,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A19,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A19,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -803,15 +803,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A20,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A20,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A20,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A20,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A20,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A20,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -826,15 +826,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A21,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A21,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A21,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A21,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A21,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A21,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -849,15 +849,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A22,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A22,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A22,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A22,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A22,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A22,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -872,15 +872,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A23,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A23,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A23,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A23,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A23,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A23,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -895,15 +895,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A24,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A24,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A24,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A24,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A24,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A24,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -918,15 +918,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A25,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A25,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A25,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A25,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A25,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A25,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -941,15 +941,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A26,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A26,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A26,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A26,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A26,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A26,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -964,15 +964,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A27,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A27,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A27,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A27,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A27,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A27,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -987,15 +987,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A28,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A28,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A28,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A28,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A28,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A28,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1010,15 +1010,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A29,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A29,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A29,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A29,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A29,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A29,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A30,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A30,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A30,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A30,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A30,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A30,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1056,15 +1056,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A31,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A31,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A31,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A31,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A31,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A31,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1079,15 +1079,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A32,Tasks!$D$2:$D$111,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A32,Tasks!$D$2:$D$118,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A32,Tasks!$D$2:$D$111,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A32,Tasks!$D$2:$D$118,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$111,$A32,Tasks!$D$2:$D$111,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$118,$A32,Tasks!$D$2:$D$118,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1109,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Confidence scoring + low-confidence to human review routing</t>
+          <t>Uploaded file bytes stored (fileData/mimeType on Document)</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -1872,7 +1872,7 @@
       <c r="E29" s="16" t="inlineStr"/>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>services/verification.js</t>
+          <t>Previously the temp file was deleted right after extraction with no copy kept anywhere — there was no way to check what you'd actually uploaded once processed</t>
         </is>
       </c>
     </row>
@@ -1887,18 +1887,18 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Extraction accuracy tuning against real-world-style documents</t>
+          <t>GET /documents/:id/file — preview/download the original upload</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr"/>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Only validated against synthetic generated images so far</t>
+          <t>Served inline with correct Content-Type; excluded from the main application/list fetch responses (.select('-fileData')) so those payloads don't balloon with binary data</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>MOCK_AI bypass — canned extraction results, no Anthropic API call</t>
+          <t>DELETE /documents/:id — remove a document outright</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -1924,7 +1924,7 @@
       <c r="E31" s="16" t="inlineStr"/>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>services/mockFixtures.js + extraction.js/rag.js. Added when ANTHROPIC_API_KEY hit a zero credit-balance error blocking all testing — lets verification/live-exception/status-transition testing continue independent of API billing state. Off by default; must not be left on for the real demo</t>
+          <t>Distinct from a targeted re-upload (which supersedes and keeps the old one for audit trail) — this actually removes it; the required item goes back to 'missing'</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Deterministic rule engine (not LLM — explainable/auditable)</t>
+          <t>Confidence scoring + low-confidence to human review routing</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -1960,21 +1960,25 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Name match check</t>
+          <t>Extraction accuracy tuning against real-world-style documents</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr"/>
-      <c r="F33" s="17" t="inlineStr"/>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Only validated against synthetic generated images so far</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="13" t="n">
@@ -1982,12 +1986,12 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>5. Cross-Verification Engine</t>
+          <t>4. Document Intelligence (OCR / AI Extraction)</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Income match check (5% tolerance)</t>
+          <t>MOCK_AI bypass — canned extraction results, no Anthropic API call</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -1996,7 +2000,11 @@
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr"/>
-      <c r="F34" s="17" t="inlineStr"/>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>services/mockFixtures.js + extraction.js/rag.js. Added when ANTHROPIC_API_KEY hit a zero credit-balance error blocking all testing — lets verification/live-exception/status-transition testing continue independent of API billing state. Off by default; must not be left on for the real demo</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="13" t="n">
@@ -2009,7 +2017,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Employer match check</t>
+          <t>Deterministic rule engine (not LLM — explainable/auditable)</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -2018,7 +2026,11 @@
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr"/>
-      <c r="F35" s="17" t="inlineStr"/>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>services/verification.js</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="13" t="n">
@@ -2031,7 +2043,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>SSN (last 4) match check</t>
+          <t>Name match check</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
@@ -2053,7 +2065,7 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Business name / DBA match check</t>
+          <t>Income match check (5% tolerance)</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -2062,11 +2074,7 @@
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr"/>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>Demonstrates the entity-name-mismatch pattern found in production loan-servicing tickets</t>
-        </is>
-      </c>
+      <c r="F37" s="17" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -2079,7 +2087,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Annual business revenue match check</t>
+          <t>Employer match check</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -2101,7 +2109,7 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Missing-document detection</t>
+          <t>SSN (last 4) match check</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -2110,11 +2118,7 @@
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr"/>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>missingDocuments() in verification.js</t>
-        </is>
-      </c>
+      <c r="F39" s="17" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -2127,7 +2131,7 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Requested-amount affordability check (auto-loan, personal-loan, small-business-loan)</t>
+          <t>Business name / DBA match check</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -2138,7 +2142,7 @@
       <c r="E40" s="16" t="inlineStr"/>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>New — compares requestedAmount against a simplified income/revenue-based estimate; flags as Warning, never auto-declines. Not a real credit/DSCR calculation</t>
+          <t>Demonstrates the entity-name-mismatch pattern found in production loan-servicing tickets</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2157,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Warning-level flags surface at the application list level, not just inside document detail</t>
+          <t>Annual business revenue match check</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -2162,11 +2166,7 @@
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr"/>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>Fixed today — routes/documents.js previously only bumped application status to Needs Review on a hard Mismatch, so an affordability warning was invisible in the officer's list view</t>
-        </is>
-      </c>
+      <c r="F41" s="17" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="13" t="n">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>US currency formatting fixed regardless of server/browser locale</t>
+          <t>Missing-document detection</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -2190,7 +2190,7 @@
       <c r="E42" s="16" t="inlineStr"/>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>toLocaleString() was rendering $3,40,000-style grouping on non-US locales; forced to 'en-US' across backend and frontend</t>
+          <t>missingDocuments() in verification.js</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>One-click 'request missing document' email to borrower</t>
+          <t>Requested-amount affordability check (auto-loan, personal-loan, small-business-loan)</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -2216,7 +2216,7 @@
       <c r="E43" s="16" t="inlineStr"/>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>Superseded by the richer in-app live-exception + targeted self-service re-upload flow — see Section 13. No email/SMS needed; the borrower sees and fixes it directly in the app</t>
+          <t>New — compares requestedAmount against a simplified income/revenue-based estimate; flags as Warning, never auto-declines. Not a real credit/DSCR calculation</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
+          <t>Warning-level flags surface at the application list level, not just inside document detail</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -2242,7 +2242,7 @@
       <c r="E44" s="16" t="inlineStr"/>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>services/rag.js</t>
+          <t>Fixed today — routes/documents.js previously only bumped application status to Needs Review on a hard Mismatch, so an affordability warning was invisible in the officer's list view</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Citation / source attribution on every answer</t>
+          <t>US currency formatting fixed regardless of server/browser locale</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -2266,7 +2266,11 @@
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr"/>
-      <c r="F45" s="17" t="inlineStr"/>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>toLocaleString() was rendering $3,40,000-style grouping on non-US locales; forced to 'en-US' across backend and frontend</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="13" t="n">
@@ -2274,12 +2278,12 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+          <t>5. Cross-Verification Engine</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Role-aware answers (officer vs. borrower)</t>
+          <t>One-click 'request missing document' email to borrower</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -2288,7 +2292,11 @@
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr"/>
-      <c r="F46" s="17" t="inlineStr"/>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>Superseded by the richer in-app live-exception + targeted self-service re-upload flow — see Section 13. No email/SMS needed; the borrower sees and fixes it directly in the app</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -2301,7 +2309,7 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
+          <t>Policy corpus grounding (full corpus in context — no vector DB yet)</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -2312,7 +2320,7 @@
       <c r="E47" s="16" t="inlineStr"/>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>Validated in data/seed/test-questions.md</t>
+          <t>services/rag.js</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2335,7 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Small-business loan Q&amp;A coverage</t>
+          <t>Citation / source attribution on every answer</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -2336,11 +2344,7 @@
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr"/>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>test-questions.md items 19-23</t>
-        </is>
-      </c>
+      <c r="F48" s="17" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -2353,20 +2357,16 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>WhatsApp channel for the assistant</t>
+          <t>Role-aware answers (officer vs. borrower)</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr"/>
-      <c r="F49" s="17" t="inlineStr">
-        <is>
-          <t>See Section 9</t>
-        </is>
-      </c>
+      <c r="F49" s="17" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="13" t="n">
@@ -2379,18 +2379,18 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
+          <t>Refusal behavior for out-of-corpus questions (no invented rates/policy)</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr"/>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>Recommended add-on from pain-point research — not yet scoped</t>
+          <t>Validated in data/seed/test-questions.md</t>
         </is>
       </c>
     </row>
@@ -2405,18 +2405,18 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Embeddings + vector search (scale-up path)</t>
+          <t>Small-business loan Q&amp;A coverage</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr"/>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
+          <t>test-questions.md items 19-23</t>
         </is>
       </c>
     </row>
@@ -2426,23 +2426,23 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Navigation shell (auth-gated stack navigation)</t>
+          <t>WhatsApp channel for the assistant</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr"/>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>App.js</t>
+          <t>See Section 9</t>
         </is>
       </c>
     </row>
@@ -2452,21 +2452,25 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Login screen</t>
+          <t>Adverse Action notice auto-drafting (policy-grounded)</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr"/>
-      <c r="F53" s="17" t="inlineStr"/>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>Recommended add-on from pain-point research — not yet scoped</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="13" t="n">
@@ -2474,23 +2478,23 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>7. Frontend — Screens &amp; Navigation</t>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Applications list screen</t>
+          <t>Embeddings + vector search (scale-up path)</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr"/>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Officer sees all; borrower sees only their own</t>
+          <t>Deliberately deferred — full corpus fits in context for the POC (ROADMAP.md)</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2509,7 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Application detail screen (header facts + tab bar)</t>
+          <t>Navigation shell (auth-gated stack navigation)</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -2516,7 +2520,7 @@
       <c r="E55" s="16" t="inlineStr"/>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>Branches fact display by product type</t>
+          <t>App.js</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2535,7 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Documents tab — upload + extracted fields display</t>
+          <t>Login screen</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -2553,7 +2557,7 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Verification tab — checks + missing documents</t>
+          <t>Applications list screen</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -2562,7 +2566,11 @@
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr"/>
-      <c r="F57" s="17" t="inlineStr"/>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>Officer sees all; borrower sees only their own</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="13" t="n">
@@ -2575,7 +2583,7 @@
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Assistant tab — chat UI with source chips</t>
+          <t>Application detail screen (header facts + tab bar)</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
@@ -2584,7 +2592,11 @@
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr"/>
-      <c r="F58" s="17" t="inlineStr"/>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>Branches fact display by product type</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="13" t="n">
@@ -2597,7 +2609,7 @@
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>Small-business-specific detail view (business name / revenue facts)</t>
+          <t>Documents tab — upload + extracted fields display</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -2619,7 +2631,7 @@
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Fintech-styled visual design pass</t>
+          <t>Verification tab — checks + missing documents</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
@@ -2628,11 +2640,7 @@
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr"/>
-      <c r="F60" s="17" t="inlineStr">
-        <is>
-          <t>Per recent commit history</t>
-        </is>
-      </c>
+      <c r="F60" s="17" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="13" t="n">
@@ -2645,7 +2653,7 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Sign-up screen (self-registration, role picker)</t>
+          <t>Assistant tab — chat UI with source chips</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
@@ -2654,11 +2662,7 @@
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr"/>
-      <c r="F61" s="17" t="inlineStr">
-        <is>
-          <t>SignUpScreen.js</t>
-        </is>
-      </c>
+      <c r="F61" s="17" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="13" t="n">
@@ -2671,7 +2675,7 @@
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>New Application screen ('Apply for a Loan')</t>
+          <t>Small-business-specific detail view (business name / revenue facts)</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
@@ -2680,11 +2684,7 @@
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr"/>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>NewApplicationScreen.js — product-type picker with conditional fields (consumer income/employer vs. business name/revenue), submits to POST /applications then lands on that application's Documents tab</t>
-        </is>
-      </c>
+      <c r="F62" s="17" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="13" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>'New application' entry point on the borrower's Applications list</t>
+          <t>Fintech-styled visual design pass</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
@@ -2708,7 +2708,7 @@
       <c r="E63" s="16" t="inlineStr"/>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>Officer role doesn't see this button — they don't file applications for themselves</t>
+          <t>Per recent commit history</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Multi-step wizard for the Apply form (Select Product -&gt; Tell Us About Yourself -&gt; Tell Us More About Yourself -&gt; Disclosures &amp; Submit)</t>
+          <t>Sign-up screen (self-registration, role picker)</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="E64" s="16" t="inlineStr"/>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Matches the real DAO intake step boundaries from Rovo research; per-step validation blocks advancing with missing required fields, progress dots show position</t>
+          <t>SignUpScreen.js</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Persistent branded header on every authenticated screen (logo, page title, profile menu)</t>
+          <t>New Application screen ('Apply for a Loan')</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
@@ -2760,7 +2760,7 @@
       <c r="E65" s="16" t="inlineStr"/>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>components/BrandHeader.js, wired globally via Stack.Navigator screenOptions.header — previously each screen had its own inconsistent title ('Application', 'Apply for a Loan') with no logo/branding and no way to sign out except from the Applications list</t>
+          <t>NewApplicationScreen.js — product-type picker with conditional fields (consumer income/employer vs. business name/revenue), submits to POST /applications then lands on that application's Documents tab</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Responsive left sidebar navigation (desktop-width viewports)</t>
+          <t>'New application' entry point on the borrower's Applications list</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -2786,7 +2786,7 @@
       <c r="E66" s="16" t="inlineStr"/>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>components/Sidebar.js — Applications / Apply for a Loan links, role-aware. Rendered outside the Stack.Navigator's own subtree so it persists across screen changes; navigates via a navigationRef (React Navigation's documented pattern for navigating from outside the navigator tree, since useNavigation() isn't available there). Hidden below 900px width — mobile/narrow-browser experience unchanged</t>
+          <t>Officer role doesn't see this button — they don't file applications for themselves</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Floating Assistant button on the application detail screen</t>
+          <t>Multi-step wizard for the Apply form (Select Product -&gt; Tell Us About Yourself -&gt; Tell Us More About Yourself -&gt; Disclosures &amp; Submit)</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
@@ -2812,7 +2812,7 @@
       <c r="E67" s="16" t="inlineStr"/>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>Bottom-right chat-bubble FAB jumps straight to the Assistant tab; hidden while already on that tab</t>
+          <t>Matches the real DAO intake step boundaries from Rovo research; per-step validation blocks advancing with missing required fields, progress dots show position</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Issue-list rendering split into individual rows (not one run-on paragraph)</t>
+          <t>Persistent branded header on every authenticated screen (logo, page title, profile menu)</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
@@ -2838,7 +2838,7 @@
       <c r="E68" s="16" t="inlineStr"/>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>See prior commit — DocumentsTab now renders each flagged check on a document as its own row</t>
+          <t>components/BrandHeader.js, wired globally via Stack.Navigator screenOptions.header — previously each screen had its own inconsistent title ('Application', 'Apply for a Loan') with no logo/branding and no way to sign out except from the Applications list</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Policy corpus — 6 markdown policies</t>
+          <t>Responsive left sidebar navigation (desktop-width viewports)</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
@@ -2864,7 +2864,7 @@
       <c r="E69" s="16" t="inlineStr"/>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
+          <t>components/Sidebar.js — Applications / Apply for a Loan links, role-aware. Rendered outside the Stack.Navigator's own subtree so it persists across screen changes; navigates via a navigationRef (React Navigation's documented pattern for navigating from outside the navigator tree, since useNavigation() isn't available there). Hidden below 900px width — mobile/narrow-browser experience unchanged</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Small Business Loan Requirements policy</t>
+          <t>Floating Assistant button on the application detail screen</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -2890,7 +2890,7 @@
       <c r="E70" s="16" t="inlineStr"/>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>data/policies/small-business-loan-requirements.md</t>
+          <t>Bottom-right chat-bubble FAB jumps straight to the Assistant tab; hidden while already on that tab</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>8. Synthetic Demo Data</t>
+          <t>7. Frontend — Screens &amp; Navigation</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
+          <t>Issue-list rendering split into individual rows (not one run-on paragraph)</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
@@ -2916,7 +2916,7 @@
       <c r="E71" s="16" t="inlineStr"/>
       <c r="F71" s="17" t="inlineStr">
         <is>
-          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
+          <t>See prior commit — DocumentsTab now renders each flagged check on a document as its own row</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Breadth/QA demo documents — Priya Nair (clean/happy-path) and Arjun Mehta (employer-mismatch warning)</t>
+          <t>Policy corpus — 6 markdown policies</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -2942,7 +2942,7 @@
       <c r="E72" s="16" t="inlineStr"/>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>Priya Nair and Arjun Mehta previously had zero document images despite being seeded applicants. Arjun's set is the only scenario exercising the softer 'warning' tier (employer differs) rather than a hard 'mismatch' — verified both against verification.js directly (Priya: overall 'pass'; Arjun: only the Employer check fires, overall 'needs-review')</t>
+          <t>Application process, document checklist, income verification, auto-loan, personal-loan, FAQ</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
+          <t>Small Business Loan Requirements policy</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
@@ -2968,7 +2968,7 @@
       <c r="E73" s="16" t="inlineStr"/>
       <c r="F73" s="17" t="inlineStr">
         <is>
-          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
+          <t>data/policies/small-business-loan-requirements.md</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Test question bank (acceptance checklist)</t>
+          <t>Consumer demo documents — Jordan Rivera (pay stub, license, bank statement)</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -2994,7 +2994,7 @@
       <c r="E74" s="16" t="inlineStr"/>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
+          <t>Planted income mismatch: $4,200 vs. $5,000 stated</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Demo script</t>
+          <t>Breadth/QA demo documents — Priya Nair (clean/happy-path) and Arjun Mehta (employer-mismatch warning)</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
@@ -3020,7 +3020,7 @@
       <c r="E75" s="16" t="inlineStr"/>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
+          <t>Priya Nair and Arjun Mehta previously had zero document images despite being seeded applicants. Arjun's set is the only scenario exercising the softer 'warning' tier (employer differs) rather than a hard 'mismatch' — verified both against verification.js directly (Priya: overall 'pass'; Arjun: only the Employer check fires, overall 'needs-review')</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Indian-named seed borrowers with real logins (Priya Nair, Arjun Mehta)</t>
+          <t>'Perfect application' pre-seeded (Priya Nair, all 3 docs uploaded + verified clean)</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
@@ -3046,7 +3046,7 @@
       <c r="E76" s="16" t="inlineStr"/>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>Priya Nair already existed as an application-only record (no login); Arjun Mehta replaces the former 'Marcus Webb' auto-loan record (safe — that name wasn't referenced in DEMO_SCRIPT.md or test-questions.md). Standing preference going forward: use Indian names for any new seed/test data added</t>
+          <t>Reuses the MOCK_AI fixture data + real verifyDocument() so it's guaranteed consistent with a live upload of the same files; includes the actual file bytes so Preview works immediately, not just an empty verification result</t>
         </is>
       </c>
     </row>
@@ -3056,23 +3056,23 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Meta developer app + free sandbox test number</t>
+          <t>Document preview/download (opens the actual uploaded file, big view, in a new tab)</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>Self-serve, free, no leadership approval needed for the demo</t>
+          <t>Authenticated blob fetch + object URL, not a plain link — the file route needs a Bearer token a plain &lt;a href&gt; can't attach. Tab opened synchronously on tap so the async fetch doesn't get popup-blocked</t>
         </is>
       </c>
     </row>
@@ -3082,21 +3082,25 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
+          <t>Document delete (with a working confirmation dialog)</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr"/>
-      <c r="F78" s="17" t="inlineStr"/>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>Checked react-native-web's actual Alert.alert source before using it — it's a documented no-op on web, would have made Delete silently do nothing when clicked in a browser. Uses window.confirm on web, Alert.alert on native</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="13" t="n">
@@ -3104,23 +3108,23 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Route inbound messages into the existing RAG assistant</t>
+          <t>'Uploaded Documents' section heading + filename shown on each document card</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>Can reuse services/rag.js — answerQuestion()</t>
+          <t>Previously a first-time viewer had no heading distinguishing the uploaded-document cards from anything else, and no way to tell which file was actually behind a given card</t>
         </is>
       </c>
     </row>
@@ -3130,21 +3134,25 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Outbound reply via WhatsApp Cloud API</t>
+          <t>Small-business demo documents — Whitfield &amp; Co. Bakery LLC</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr"/>
-      <c r="F80" s="17" t="inlineStr"/>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>Tax return, personal financial statement, business license, ownership disclosure; planted revenue mismatch ($275,400 vs. $340,000) and entity-name mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="13" t="n">
@@ -3152,23 +3160,23 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>9. WhatsApp Integration</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Production Meta Business verification</t>
+          <t>Test question bank (acceptance checklist)</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr"/>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
+          <t>data/seed/test-questions.md — 23 questions across both scenarios</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3186,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Render Blueprint configuration</t>
+          <t>Demo script</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
@@ -3194,7 +3202,7 @@
       <c r="E82" s="16" t="inlineStr"/>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>render.yaml — backend web service + frontend static site</t>
+          <t>docs/DEMO_SCRIPT.md — leads with the small-business scenario</t>
         </is>
       </c>
     </row>
@@ -3204,23 +3212,23 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>8. Synthetic Demo Data</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Backend deployed &amp; health-checked on Render</t>
+          <t>Indian-named seed borrowers with real logins (Priya Nair, Arjun Mehta)</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr"/>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>Confirm live and reachable before demo day (/health)</t>
+          <t>Priya Nair already existed as an application-only record (no login); Arjun Mehta replaces the former 'Marcus Webb' auto-loan record (safe — that name wasn't referenced in DEMO_SCRIPT.md or test-questions.md). Standing preference going forward: use Indian names for any new seed/test data added</t>
         </is>
       </c>
     </row>
@@ -3230,23 +3238,23 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Frontend deployed as Render static site</t>
+          <t>Meta developer app + free sandbox test number</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr"/>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Confirm Expo web export + rewrite rule are working</t>
+          <t>Self-serve, free, no leadership approval needed for the demo</t>
         </is>
       </c>
     </row>
@@ -3256,25 +3264,21 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
+          <t>Webhook endpoint to receive inbound WhatsApp messages</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr"/>
-      <c r="F85" s="17" t="inlineStr">
-        <is>
-          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
-        </is>
-      </c>
+      <c r="F85" s="17" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="13" t="n">
@@ -3282,23 +3286,23 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>10. Hosting &amp; Deployment</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
+          <t>Route inbound messages into the existing RAG assistant</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E86" s="16" t="inlineStr"/>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+          <t>Can reuse services/rag.js — answerQuestion()</t>
         </is>
       </c>
     </row>
@@ -3308,25 +3312,21 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Manual acceptance test question bank</t>
+          <t>Outbound reply via WhatsApp Cloud API</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr"/>
-      <c r="F87" s="17" t="inlineStr">
-        <is>
-          <t>23 questions across consumer + small-business scenarios</t>
-        </is>
-      </c>
+      <c r="F87" s="17" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="13" t="n">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>9. WhatsApp Integration</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Automated unit/integration tests</t>
+          <t>Production Meta Business verification</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
@@ -3348,7 +3348,11 @@
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr"/>
-      <c r="F88" s="17" t="inlineStr"/>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>Only needed post-demo, for a real bank pilot — not for the MVP</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="13" t="n">
@@ -3356,23 +3360,23 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>End-to-end demo rehearsal (full run-through, timed)</t>
+          <t>Render Blueprint configuration</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr"/>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>Schedule before presentation day</t>
+          <t>render.yaml — backend web service + frontend static site</t>
         </is>
       </c>
     </row>
@@ -3382,21 +3386,25 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>11. Testing &amp; QA</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Cross-browser / device check (Expo web export)</t>
+          <t>Backend deployed &amp; health-checked on Render</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr"/>
-      <c r="F90" s="17" t="inlineStr"/>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>Confirm live and reachable before demo day (/health)</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="13" t="n">
@@ -3404,21 +3412,25 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>README (quick start, architecture, deploy steps)</t>
+          <t>Frontend deployed as Render static site</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr"/>
-      <c r="F91" s="17" t="inlineStr"/>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>Confirm Expo web export + rewrite rule are working</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="13" t="n">
@@ -3426,21 +3438,25 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>ROADMAP.md (phased build plan)</t>
+          <t>MongoDB Atlas cluster provisioned (M0 free tier)</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr"/>
-      <c r="F92" s="17" t="inlineStr"/>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>Confirm connection string + Network Access 0.0.0.0/0 are set</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="13" t="n">
@@ -3448,12 +3464,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>10. Hosting &amp; Deployment</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
+          <t>One-shot /admin/reset endpoint for pre-demo data reset</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
@@ -3462,7 +3478,11 @@
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr"/>
-      <c r="F93" s="17" t="inlineStr"/>
+      <c r="F93" s="17" t="inlineStr">
+        <is>
+          <t>routes/admin.js — seeds + re-indexes policies in one call</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="13" t="n">
@@ -3470,12 +3490,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>12. Documentation</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Development task tracker (this file)</t>
+          <t>Manual acceptance test question bank</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
@@ -3486,7 +3506,7 @@
       <c r="E94" s="16" t="inlineStr"/>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
+          <t>23 questions across consumer + small-business scenarios</t>
         </is>
       </c>
     </row>
@@ -3496,25 +3516,21 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
+          <t>Automated unit/integration tests</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr"/>
-      <c r="F95" s="17" t="inlineStr">
-        <is>
-          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
-        </is>
-      </c>
+      <c r="F95" s="17" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="13" t="n">
@@ -3522,23 +3538,23 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
+          <t>End-to-end demo rehearsal (full run-through, timed)</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E96" s="16" t="inlineStr"/>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
+          <t>Schedule before presentation day</t>
         </is>
       </c>
     </row>
@@ -3548,25 +3564,21 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>11. Testing &amp; QA</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
+          <t>Cross-browser / device check (Expo web export)</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E97" s="16" t="inlineStr"/>
-      <c r="F97" s="17" t="inlineStr">
-        <is>
-          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
-        </is>
-      </c>
+      <c r="F97" s="17" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="13" t="n">
@@ -3574,12 +3586,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Document supersede/audit-trail model (current vs. superseded)</t>
+          <t>README (quick start, architecture, deploy steps)</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
@@ -3588,11 +3600,7 @@
         </is>
       </c>
       <c r="E98" s="16" t="inlineStr"/>
-      <c r="F98" s="17" t="inlineStr">
-        <is>
-          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
-        </is>
-      </c>
+      <c r="F98" s="17" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="13" t="n">
@@ -3600,12 +3608,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
+          <t>ROADMAP.md (phased build plan)</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -3614,11 +3622,7 @@
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr"/>
-      <c r="F99" s="17" t="inlineStr">
-        <is>
-          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
-        </is>
-      </c>
+      <c r="F99" s="17" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="13" t="n">
@@ -3626,12 +3630,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
+          <t>DEMO_SCRIPT.md (3-minute walkthrough)</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
@@ -3640,11 +3644,7 @@
         </is>
       </c>
       <c r="E100" s="16" t="inlineStr"/>
-      <c r="F100" s="17" t="inlineStr">
-        <is>
-          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
-        </is>
-      </c>
+      <c r="F100" s="17" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="13" t="n">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+          <t>12. Documentation</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>RAG assistant reflects only current, unresolved exceptions</t>
+          <t>Development task tracker (this file)</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -3668,7 +3668,7 @@
       <c r="E101" s="16" t="inlineStr"/>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
+          <t>Prepared 2026-09-11, moved to Excel — update statuses as work progresses</t>
         </is>
       </c>
     </row>
@@ -3683,18 +3683,18 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>In-browser instant document classification &amp; quality check at upload</t>
+          <t>Unified 'Action needed' list — every open issue (missing or flagged) in one place</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E102" s="16" t="inlineStr"/>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
+          <t>New openExceptions() in verification.js; returned by GET /applications/:id; rendered as a card at the top of the Documents tab</t>
         </is>
       </c>
     </row>
@@ -3709,18 +3709,18 @@
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Pre-submission completeness check (required schedules/pages present)</t>
+          <t>Targeted self-service re-upload — fix exactly one flagged/missing item, no restart</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E103" s="16" t="inlineStr"/>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>Per document type</t>
+          <t>expectedDocType passed on upload; this is the in-app equivalent of the 'SMS/magic-link' concept — same outcome, no external channel needed since it's already inside the app</t>
         </is>
       </c>
     </row>
@@ -3735,18 +3735,18 @@
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Blur / glare / legibility detection before accepting an upload</t>
+          <t>Wrong-file-type caught immediately during a targeted re-upload</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E104" s="16" t="inlineStr"/>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>Complements existing confidence-score routing in verification.js</t>
+          <t>New 'Document type' check in verifyDocument() when expectedDocType doesn't match the classified docType</t>
         </is>
       </c>
     </row>
@@ -3761,18 +3761,18 @@
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+          <t>Document supersede/audit-trail model (current vs. superseded)</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E105" s="16" t="inlineStr"/>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+          <t>Document.status field; fixing an item replaces it instead of leaving a duplicate; superseded docs kept for audit, hidden by default behind 'Show document history'</t>
         </is>
       </c>
     </row>
@@ -3782,23 +3782,23 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+          <t>Application status self-heals (Needs Review -&gt; Submitted) once every exception clears</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E106" s="16" t="inlineStr"/>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>routes/documents.js — no manual officer action required to un-flag a resolved application</t>
         </is>
       </c>
     </row>
@@ -3808,23 +3808,23 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+          <t>Borrower upload endpoint scoped to their own application (auth fix)</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E107" s="16" t="inlineStr"/>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+          <t>POST /documents/:applicationId had no ownership check before today — any authenticated borrower could upload to any applicationId. Now matches the same check already used on GET /applications/:id</t>
         </is>
       </c>
     </row>
@@ -3834,23 +3834,23 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Shared visibility for all parties on one application</t>
+          <t>RAG assistant reflects only current, unresolved exceptions</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E108" s="16" t="inlineStr"/>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+          <t>rag.js's applicationStateSummary was reading ALL documents including superseded ones — a resolved issue could be re-surfaced in an answer as if still open. Fixed to use only current documents + the same openExceptions list the UI shows</t>
         </is>
       </c>
     </row>
@@ -3860,12 +3860,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+          <t>In-browser instant document classification &amp; quality check at upload</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr">
@@ -3876,7 +3876,7 @@
       <c r="E109" s="16" t="inlineStr"/>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+          <t>Client-side pre-submission check, before the file is even sent — different from the (built) post-upload flagging</t>
         </is>
       </c>
     </row>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+          <t>Pre-submission completeness check (required schedules/pages present)</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr">
@@ -3902,7 +3902,7 @@
       <c r="E110" s="16" t="inlineStr"/>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+          <t>Per document type</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>Self-service grace period / split-payment offers</t>
+          <t>Blur / glare / legibility detection before accepting an upload</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr">
@@ -3928,13 +3928,195 @@
       <c r="E111" s="16" t="inlineStr"/>
       <c r="F111" s="17" t="inlineStr">
         <is>
+          <t>Complements existing confidence-score routing in verification.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="13" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>13. Real-Time Document Validation &amp; Self-Service Re-Request (DocuSense)</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Auto pre-fill of underwriting review fields from extracted data</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E112" s="16" t="inlineStr"/>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>Extraction already produces the data; pre-filling a review form UI is net-new</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>Step-by-step milestone tracker UI (Intake -&gt; Doc Verification -&gt; Underwriting -&gt; Closing -&gt; Disbursement)</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr"/>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="13" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Multi-party checklist — per-owner/signer verification status for business loans</t>
+        </is>
+      </c>
+      <c r="D114" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="inlineStr"/>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>Builds on the ownership-disclosure doc type; needs a per-owner sub-record, not just one applicant</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="13" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>Shared visibility for all parties on one application</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="inlineStr"/>
+      <c r="F115" s="17" t="inlineStr">
+        <is>
+          <t>Officer and the single applicant now see the exact same live exception list (built in Section 13's live-exception flow) — what's still missing is MULTIPLE distinct people (co-owners/guarantors) on one application; auth model currently ties an application to one applicant email only</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>14. Multi-Party &amp; Milestone Tracking (Lending Co-Pilot)</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>Core-readiness / entity-name pre-validator earlier in the flow</t>
+        </is>
+      </c>
+      <c r="D116" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="inlineStr"/>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>Extends the Section 5 business-name check to run at intake, before final closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="13" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="inlineStr">
+        <is>
+          <t>Cash-flow dip / pre-delinquency risk detection from transaction history</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="inlineStr"/>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t>Different lifecycle stage (servicing, not origination) — needs a transaction-history data model not in the current schema. Recommend as roadmap/vision talking point, not a 4-week build target</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>15. Predictive Servicing (EarlyCare) — Post-MVP</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>Self-service grace period / split-payment offers</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="inlineStr"/>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F111"/>
-  <conditionalFormatting sqref="D2:D111">
+  <autoFilter ref="A1:F118"/>
+  <conditionalFormatting sqref="D2:D118">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -3946,7 +4128,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3960,7 +4142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4849,9 +5031,149 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Document preview/delete</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Preview opens the actual uploaded file in a new tab</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Tap Preview on any uploaded document card.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>A new tab opens showing the real image/PDF that was uploaded, not a placeholder — usable to check you uploaded the right file.</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Directly answers 'how do I know what I actually uploaded' — previously there was no way to check at all once a file was processed.</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Document preview/delete</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Delete removes a document and the item goes back to missing</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Tap Delete on an uploaded document, confirm the dialog.</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>The document disappears from Uploaded Documents; the corresponding Required Documents row goes back to Pending.</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>A genuinely destructive, different action from a targeted re-upload (which supersedes and keeps history) — confirmation dialog matters here specifically.</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Document preview/delete</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Delete's confirmation dialog actually appears on web</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Tap Delete in a browser (not the native app).</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>A confirm dialog appears (window.confirm), not silence.</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Caught before shipping: react-native-web's Alert.alert is a no-op on web — using it directly would have made Delete silently do nothing when clicked in a browser, with no error and no visible failure.</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Perfect application</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Priya Nair's application shows zero action-needed items out of the box</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Log in as officer or priya.nair@example.demo right after a fresh seed/reset — no manual upload needed.</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>All 3 required documents show 'Received', Action Needed is empty, application status is 'Submitted' (not 'Needs Review').</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>A reference 'everything's correct' example to compare against, without depending on the user manually finding and uploading the exact right 3 files themselves first.</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code, needs a live click-through once real MongoDB/Claude credentials exist</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
-  <conditionalFormatting sqref="G2:G25">
+  <autoFilter ref="A1:G29"/>
+  <conditionalFormatting sqref="G2:G29">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>LEFT($G2,3)="Yes"</formula>
     </cfRule>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -655,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
@@ -669,6 +671,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -700,15 +703,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -716,6 +719,8 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -757,15 +762,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A18,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A18,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A18,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A18,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A18,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A18,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -780,15 +785,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A19,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A19,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A19,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A19,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A19,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A19,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -803,15 +808,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A20,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A20,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A20,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A20,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A20,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A20,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -826,15 +831,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A21,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A21,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A21,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A21,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A21,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A21,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -849,15 +854,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A22,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A22,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A22,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A22,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A22,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A22,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -872,15 +877,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A23,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A23,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A23,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A23,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A23,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A23,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -895,15 +900,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A24,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A24,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A24,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A24,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A24,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A24,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -918,15 +923,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A25,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A25,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A25,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A25,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A25,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A25,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -941,15 +946,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A26,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A26,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A26,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A26,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A26,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A26,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -964,15 +969,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A27,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A27,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A27,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A27,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A27,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A27,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -987,15 +992,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A28,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A28,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A28,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A28,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A28,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A28,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1010,15 +1015,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A29,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A29,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A29,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A29,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A29,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A29,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1033,15 +1038,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A30,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A30,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A30,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A30,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A30,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A30,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1056,15 +1061,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A31,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A31,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A31,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A31,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A31,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A31,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1079,19 +1084,65 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A32,Tasks!$D$2:$D$118,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A32,Tasks!$D$2:$D$133,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A32,Tasks!$D$2:$D$118,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A32,Tasks!$D$2:$D$133,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$118,$A32,Tasks!$D$2:$D$118,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A32,Tasks!$D$2:$D$133,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
         <f>SUM(B32:D32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A33,Tasks!$D$2:$D$133,"Completed")</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A33,Tasks!$D$2:$D$133,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A33,Tasks!$D$2:$D$133,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="E33">
+        <f>SUM(B33:D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A34,Tasks!$D$2:$D$133,"Completed")</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A34,Tasks!$D$2:$D$133,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>COUNTIFS(Tasks!$B$2:$B$133,$A34,Tasks!$D$2:$D$133,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>SUM(B34:D34)</f>
         <v/>
       </c>
     </row>
@@ -1109,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4111,6 +4162,381 @@
       <c r="F118" s="17" t="inlineStr">
         <is>
           <t>Same caveat as above — deprioritize for the MVP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5. Cross-Verification Engine</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cross-document check: bank statement deposit vs. pay stub net pay (amount + employer-name match)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>backend/src/services/verification.js — crossDocumentChecks()/withCrossDocumentChecks(); catches an inflated pay stub not backed by a real deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5. Cross-Verification Engine</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Statutory payroll-math check: Social Security (6.2%) &amp; Medicare (1.45%) withholding vs. gross pay</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>backend/src/services/verification.js; flat federal rates, not income-tax brackets (deliberately not modeled — see Section 16 note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5. Cross-Verification Engine</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Year-to-date gross consistency check (YTD gross ÷ pay period # vs. current period gross)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>backend/src/services/verification.js; pay stub images regenerated to show YTD gross + period #</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5. Cross-Verification Engine</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ownership percentage sanity bound (0-100%)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>backend/src/services/verification.js; single-doc-per-application model limits this to a bounds check, not a multi-owner sum-to-100% check</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5. Cross-Verification Engine</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Personal financial statement vs. bank statement cash-on-hand cross-check</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Same buildable pattern as the completed pay-stub/bank-statement check above — no vendor needed, just not yet prioritized</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PDF metadata / edit-history forensics</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>No vendor cost, but our demo docs are images (no metadata to inspect); even on real PDFs this is easily defeated by re-export/screenshot — low reliability even in production</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Font/glyph and template-mismatch detection</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Needs a reference library of genuine payroll-provider templates (ADP/Gusto/Paychex) — a real computer-vision project, out of hackathon scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Error Level Analysis (ELA) for spliced/edited images</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Free to build (no vendor), but only detects JPEG recompression artifacts — has no effect on our PNG uploads; revisit if real photographed/scanned uploads are supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Identity verification (IDV) for driver's license / government ID</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>NEEDS REAL-TIME API KEY + FUNDING — vendor options: Persona, Onfido, Jumio, ID.me (liveness + barcode/MRZ check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>IRS tax transcript verification (Form 4506-C / IVES) for business tax returns</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NEEDS FUNDING — requires becoming an approved IVES participant; not obtainable via a simple developer API key sign-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Business registry / EIN verification (Secretary of State lookup)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NEEDS REAL-TIME API KEY + FUNDING — vendor option: Middesk (most state registries have no free structured API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>16. Document Authenticity — Digital Forensics &amp; Direct-Source Verification</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Direct-from-source payroll verification (bypass documents entirely)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NEEDS REAL-TIME API KEY + FUNDING — vendor options: Argyle, Pinwheel, Plaid Income; this is the actual production-grade fix — uploaded documents become an optional fallback, not the source of truth</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>OFAC sanctions / PEP screening for beneficial owners</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>FREE — U.S. Treasury OFAC SDN list is a public, free, downloadable dataset; no paid vendor required to build a basic screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Address verification (standardization + deliverability)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>FREE TIER AVAILABLE — USPS Web Tools API has a no-cost tier suitable for this use case</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Credit bureau pull / existing-loan (trade line) check</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>NEEDS FUNDING — real bureau access (Equifax/Experian/TransUnion) requires a licensed FCRA "permissible purpose" relationship, not just an API key; soft-pull aggregators (Array, Bloom Credit, MeridianLink) are the realistic funded path</t>
         </is>
       </c>
     </row>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -10,10 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal vs Built" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Proposal vs Built'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -610,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -645,7 +647,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Khavya Sakthivel &amp; Sukumar Dhandapani (Development) · Souvik Das (QA)</t>
+          <t>Khavya Sakthivel &amp; Sukumar Dhandapani (Development) · Souvik Das (QA) — updated 2026-10-22 (sections 18–20 added)</t>
         </is>
       </c>
     </row>
@@ -703,15 +705,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -762,15 +764,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A18,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A18,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A18,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A18,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A18,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A18,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -785,15 +787,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A19,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A19,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A19,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A19,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A19,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A19,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -808,15 +810,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A20,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A20,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A20,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A20,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A20,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A20,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -831,15 +833,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A21,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A21,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A21,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A21,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A21,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A21,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -854,15 +856,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A22,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A22,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A22,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A22,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A22,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A22,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -877,15 +879,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A23,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A23,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A23,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A23,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A23,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A23,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -900,15 +902,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A24,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A24,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A24,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A24,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A24,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A24,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -923,15 +925,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A25,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A25,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A25,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A25,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A25,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A25,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -946,15 +948,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A26,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A26,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A26,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A26,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A26,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A26,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -969,15 +971,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A27,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A27,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A27,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A27,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A27,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A27,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -992,15 +994,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A28,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A28,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A28,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A28,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A28,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A28,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1015,15 +1017,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A29,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A29,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A29,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A29,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A29,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A29,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1038,15 +1040,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A30,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A30,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A30,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A30,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A30,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A30,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1061,15 +1063,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A31,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A31,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A31,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A31,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A31,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A31,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1084,15 +1086,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A32,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A32,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A32,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A32,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A32,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A32,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1107,15 +1109,15 @@
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A33,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A33,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A33,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A33,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A33,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A33,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E33">
@@ -1130,19 +1132,88 @@
         </is>
       </c>
       <c r="B34">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A34,Tasks!$D$2:$D$133,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A34,Tasks!$D$2:$D$189,"Completed")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A34,Tasks!$D$2:$D$133,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A34,Tasks!$D$2:$D$189,"In Progress")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>COUNTIFS(Tasks!$B$2:$B$133,$A34,Tasks!$D$2:$D$133,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A34,Tasks!$D$2:$D$189,"Not Started")</f>
         <v/>
       </c>
       <c r="E34">
         <f>SUM(B34:D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="B35">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A35,Tasks!$D$2:$D$189,"Completed")</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A35,Tasks!$D$2:$D$189,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="D35">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A35,Tasks!$D$2:$D$189,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>SUM(B35:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="B36">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A36,Tasks!$D$2:$D$189,"Completed")</f>
+        <v/>
+      </c>
+      <c r="C36">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A36,Tasks!$D$2:$D$189,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="D36">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A36,Tasks!$D$2:$D$189,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="E36">
+        <f>SUM(B36:D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A37,Tasks!$D$2:$D$189,"Completed")</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A37,Tasks!$D$2:$D$189,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="D37">
+        <f>COUNTIFS(Tasks!$B$2:$B$189,$A37,Tasks!$D$2:$D$189,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>SUM(B37:D37)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2519,7 +2590,7 @@
       <c r="E53" s="16" t="inlineStr"/>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>Recommended add-on from pain-point research — not yet scoped</t>
+          <t>Recommended add-on from pain-point research — not yet scoped [2026-10-22] A template decline notice (ECOA wording) is shown to borrowers on rejection; a compliant adverse-action notice is tracked in Section 18.</t>
         </is>
       </c>
     </row>
@@ -3577,11 +3648,15 @@
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr"/>
-      <c r="F95" s="17" t="inlineStr"/>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>Backend suite: 61 tests (verification, statement analysis, RAG grounding, decision rules, borrower-view privacy); 60 pass, 1 pre-existing failure (test/rag/serviceClients.test.js imports a missing export). No frontend or route-level tests yet.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="13" t="n">
@@ -4025,13 +4100,13 @@
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E113" s="16" t="inlineStr"/>
       <c r="F113" s="17" t="inlineStr">
         <is>
-          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum</t>
+          <t>New status model, beyond the current submitted/needs-review/approved/rejected enum [2026-10-22] A Progress page now shows a derived 6-step timeline (submitted &gt; documents &gt; verification &gt; issues &gt; officer review &gt; decision) with a "You are here" marker. Still missing: a persisted milestone status model and the closing / disbursement stages.</t>
         </is>
       </c>
     </row>
@@ -4536,13 +4611,1413 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NEEDS FUNDING — real bureau access (Equifax/Experian/TransUnion) requires a licensed FCRA "permissible purpose" relationship, not just an API key; soft-pull aggregators (Array, Bloom Credit, MeridianLink) are the realistic funded path</t>
+          <t>NEEDS FUNDING — real bureau access (Equifax/Experian/TransUnion) requires a licensed FCRA "permissible purpose" relationship, not just an API key; soft-pull aggregators (Array, Bloom Credit, MeridianLink) are the realistic funded path [2026-10-22] Interim: staff enter the credit score by hand on the Decision page (Section 18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>7. Frontend — Screens &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Verification checklist on the Documents tab — every check (matches and flags) per document, plus an application-wide summary</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>components/VerificationSummary.js. Answers the jury question "what parameters are checked": expected value next to value found, cross-document checks tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>7. Frontend — Screens &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>One readable URL per application page: /applications/:id/{progress,documents,verification,action-needed,assistant,decision}</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>App.js linking config; browser tab title names the page. AuthContext now waits for the saved session so a reload keeps the deep link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>7. Frontend — Screens &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Progress page — % complete, "You are here" timeline, next step</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ProgressTab.js, utils/progress.js. Derived from documents, verification and status; no new backend state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>7. Frontend — Screens &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Action Needed page — open items with one-tap upload / re-upload</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ActionNeededTab.js; tab shows the open count. Upload logic extracted to utils/uploadDocument.js.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>7. Frontend — Screens &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Assistant as a full page, sidebar "Ask LoanLens" entry and per-application sidebar sub-navigation</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>The floating launcher is hidden on the Assistant page (it covered Send). chatBus.js lets the sidebar open the chat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Chat answers application-state questions from real data and opens the matching page</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>assistantActions.js: documents / progress / verification / action needed (+ decision for staff). No AI credits needed. Questions naming another person go to the server, which enforces access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>6. RAG Assistant (Conversational Q&amp;A)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Grouped sample questions in the chat (documents, progress, verification, policy; officer and underwriter sets)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>AssistantTab.js. Policy-source navigation with sentence highlighting is Section 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>10. Hosting &amp; Deployment</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Anthropic API credits / billing — IT ticket #2166509</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Key returns HTTP 400 "credit balance too low"; Console shows $0.00 on the Evaluation plan. Blocks live extraction and the AI assistant. backend/check-credits.js reproduces it. Meanwhile use MOCK_AI=true or the Groq provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>10. Hosting &amp; Deployment</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Rotate the Anthropic API key (it was visible in a screenshot) and update backend/.env and the Render environment</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Do this once billing is active. The key must only live in .env, never in .env.example.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>12. Documentation</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Reconcile LoanLensAI_RAG_Implementation_Plan.xlsx statuses with the code</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>All 83 tasks read "Not Started" although R2 file storage and several RAG commits landed after 2026-10-02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>12. Documentation</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ask Rovo / ThoughtFocus mentor questions Q01–Q13 and record the answers</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Rovo Questions sheet of the RAG plan: all 13 still "Open", no answers. Priority: Q01 (approved cloud account), Q02 (third-party policy), Q03/Q04 (tenant isolation), Q06 (approved embeddings), Q09 (RAG evaluation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>12. Documentation</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Document "Proposal vs Built" for the pitch (see the new sheet in this workbook) and the stack deviation (FastAPI/Azure vs Node/Claude)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Sheet added 2026-10-22; keep it current so the demo never claims an unbuilt feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Underwriter role — seeded login, not self-registrable, read-only on documents</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>underwriter@loanlens.demo. config/roles.js; self-registration still only offers officer / borrower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Decision endpoint: approve / decline / refer / return, enforced by role and application state</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>POST /applications/:id/decision; all rules in services/decisionRules.js. Before this, nothing in the app could set approved or rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Policy-parameter assessment: documents, identity, income, credit score, affordability — waivable vs non-waivable</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Only credit score and affordability can be waived. Name / SSN / document-type / income mismatches and missing documents can only be fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Credit score entry by staff, locked to whoever currently holds the file</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>PUT /applications/:id/credit-score; manual entry (no bureau pull). Officer before referral, underwriter while referred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Exception approval: waived parameters, compensating factors, "who knows the borrower" note, conditions of approval</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Compensating factors required (20+ chars); every unmet parameter must be named.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Append-only audit trail of every review action (who, role, when, note, details)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Application.reviewHistory; shown on the Decision page. Covers decisions only — extraction events are in Section 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Borrower-safe view: outcome, reasons or conditions only — never the score, audit trail or exception rationale</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>forViewer() + borrowerNotice(); unit-tested on the real functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Documents locked while an application is referred or decided</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>documents.js upload / delete return 409; underwriter can preview files but not change them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Staff-only Decision page, "With Underwriter" status, Underwriter portal heading, staff chat questions</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DecisionTab.js. Tested in the browser against a mock API that uses the real rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Unit tests for decision rules and borrower-view privacy</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>backend/test/decisions/ — 21 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Confirm the real minimum credit score per product with the bank</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>NEEDS INPUT — 620 (auto) / 660 (personal) / 680 (business) in config/underwriting.js are demo placeholders. Also add the "Credit Checks &amp; Credit Score Policy" document (Section 20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Click-through of the full officer &gt; underwriter &gt; borrower flow on real MongoDB</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Only unit tests and a mock API so far. Run npm run reset first (adds the underwriter and Arjun Mehta score 598).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Add the credit-exception scenario to DEMO_SCRIPT.md</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Arjun Mehta (score 598): officer cannot approve, refers, underwriter approves with an exception, borrower sees only the outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Notify on referral and decision (email / in-app)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Policy text already promises notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Underwriter queue view — referred files first, with filters</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Underwriters currently see every application; referred ones show "With Underwriter".</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Approval limits / dual control (second approver above a loan amount)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Typical bank control; not in the proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Appeals — re-open a decided application</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>A decided application is currently immutable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Compliant adverse-action notice (ECOA / Reg B): creditor details, bureau disclosure when a report was used, delivery deadline</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Current notice is generic template wording — needs compliance review. Related to task 52.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>18. Loan Decision &amp; Underwriter Exception Workflow</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Co-signer / guarantor role (borrower-side, liable, submits own documents)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Different from the underwriter: a person who vouches AND signs. Needs the multi-party model in Section 14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Binder dump: auto-split and classify a large mixed PDF (200–500 pages)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Headline feature of the submission. Today one upload is treated as one document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>TILA / RESPA disclosure-timing compliance checks</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Promised in the submission; no rule or data exists yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MISMO-standard JSON output for LOS integration</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Phase 3 in the submission; legitimately later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Cross-document address check (application vs licence / pay stub / bank statement)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Submission promised name, SSN, income and address. Address is extracted but not compared. Distinct from task 131 (USPS validation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Complete audit trail of every extraction and decision</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Decisions and credit-score entries are logged (Section 18). Uploads, extractions and re-verifications are not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Multi-tenant SaaS: per-bank tenancy and policy indexing</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>RAG plan phase P2; the app is single-bank today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>GLBA / SOC 2-aligned controls: encryption at rest, zero-retention LLM terms, access logging</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Submission risk-mitigation promise; only role-based access exists today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Pay stub / bank statement recency check (policy: within 30 days)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Policy and FAQ say older documents are rejected; verification.js has no date check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ID expiry check (policy: expired IDs are not accepted)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>No expiry field is extracted or checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Edit an application after submission (FAQ says borrowers can)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>No edit endpoint or screen exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Reconcile policy text with code: payment ratios (policy 3x / 45% vs code 15% / 20%) and term options</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Answers currently quote the policy numbers, not the ones the system enforces. See docs/POLICY_COVERAGE_AND_QUESTIONS.md section 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Auto loan: capture vehicle value / purchase document for the "110% of book value" rule</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Policy states the limit; no field or document supports it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>19. Proposal Gaps — Promised in Submission, Not Yet Built</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Review policy promises the product does not keep (email notice, rejection of blurry documents)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Either build the behaviour or reword the policy; list in POLICY_COVERAGE_AND_QUESTIONS.md section 1b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Check which policy documents are actually live in the admin panel and compare with the required list</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Uploads are stored only as Chroma chunks; GET /rag-admin/documents (admin login) lists them. Not readable from the dev machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Policy document: Interest Rates, Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Priority 1. Router already sends rate / fee questions to policy; no document exists. Must not quote specific rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Policy document: Repayment, Prepayment &amp; Foreclosure</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Priority 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Policy document: Credit Checks &amp; Credit Score Policy</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Priority 1. Also supplies the minimum scores used by the underwriter workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Policy document: Co-signers &amp; Joint Applicants</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Priority 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Policy document: Collateral &amp; Vehicle Requirements (auto)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Priority 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Policy document: Adverse Action, Denial Reasons &amp; Appeals</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Priority 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Policy documents, priority 2: late payment &amp; hardship, privacy &amp; retention, closing &amp; disbursement, contact &amp; escalation, eligibility by employment type</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>See POLICY_COVERAGE_AND_QUESTIONS.md section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Remove the "Fictional policy… synthetic content" banner line from every policy file</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>It lands inside the first retrieved chunk and can be quoted in answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Policy read API: list documents and return chunks in order (any logged-in user)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Needed by the policy page; getCollectionRecords must also request document text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Policy page: open the cited policy, highlight the matching sentence, link from chat sources and sidebar</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Design in POLICY_COVERAGE_AND_QUESTIONS.md section 5. Open decision: which policies borrowers may see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>20. Policy Documents &amp; Policy Page</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Add the 55 question scenarios to data/seed/test-questions.md and run them</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Covers policy, own-application, mixed, follow-up, refuse and officer questions.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F118"/>
-  <conditionalFormatting sqref="D2:D118">
+  <autoFilter ref="A1:F189"/>
+  <conditionalFormatting sqref="D2:D189">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -4554,7 +6029,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D189" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4568,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5597,9 +7072,394 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Verification checklist</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Documents tab lists every check, matches and flags</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Upload any document and look at its card on the Documents tab.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>A "Verification checks" block shows "N fields extracted · M checks run · X matched · Y flagged" and one row per check with expected vs found. An application-wide summary sits above the documents.</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>The jury asked to see which parameters are verified, not only the problems.</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>Yes — previewed in the browser with sample data; a real upload has not been clicked through</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Page URLs</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>A reload keeps you on the same application page</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Open /applications/&lt;id&gt;/progress while logged in and reload the browser.</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>You stay on the Progress page; the tab title reads "LoanLens AI · Application · Progress".</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Pages can be bookmarked and shared; the chat can open them.</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>Yes — browser against a mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Chat navigation</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>"What documents have I uploaded?" opens the Documents page</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Open the chat and ask the question (or click the sample question).</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>The answer lists the uploaded documents and any still needed, and the Documents page opens with an "Opened Documents" link.</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Chat becomes a way to navigate, and the answer comes from real data, not the AI.</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>Yes — browser against a mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Chat navigation</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Asking from the Assistant page does not lose the conversation</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>On the Assistant page ask "What is the progress of my application?".</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>The answer stays on the page with an "Open Progress" link instead of navigating away.</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Navigating would unmount the chat and lose the conversation.</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>Yes — browser against a mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Decision workflow</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Loan officer cannot approve a file whose credit score is below the minimum</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Record a score of 598 on a personal-loan file (minimum 660) and try to approve.</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Approve is disabled and the API returns 422 "Refer it to the underwriter for an exception". Referring is offered.</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>The core of the exception process: an officer cannot approve past a parameter.</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit tests and mock API; not on real MongoDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Decision workflow</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>An exception needs a justification, compensating factors and every unmet parameter named</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>As officer refer with a 2-character note; as underwriter approve without compensating factors.</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Both are refused with a specific message; with proper text the referral and the exception approval succeed.</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>Stops "ok" from being a reason for waiving a bank rule.</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Decision workflow</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>A non-waivable mismatch can never be referred or waived</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Use a file with an SSN or name mismatch and a low credit score; try to refer, then (as underwriter) waive "identity".</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Referral and waiver are refused: the borrower must correct the mismatch.</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>An exception is for a short borrower, not for documents that disagree about who the borrower is.</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Decision workflow</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Credit score cannot be changed after referral by the officer</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Refer a file, then as officer try to change the score.</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>409; only the underwriter can change it while the file is referred.</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>The officer must not alter what the underwriter is judging.</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit tests and mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Decision workflow</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Borrower never sees the credit score, audit trail or exception rationale</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Approve a file as an exception, then fetch it as the borrower.</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Only the outcome and the conditions are returned; no score, history, waived parameters or relationship note.</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>Internal rationale and a borrower's credit data must stay with bank staff.</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit tests on the real functions and mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Decision workflow</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Documents are locked while a file is referred or decided</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Refer a file, then as the borrower try to upload or delete a document.</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>409 with the reason; the underwriter can still preview files but not change them.</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>The documents are the record the decision rests on.</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — implemented in code; needs a live test on real MongoDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Decision workflow</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Underwriter login works and cannot be self-registered</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Run npm run reset, sign in as underwriter@loanlens.demo, then try to register with role underwriter.</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Login succeeds with the Underwriter portal heading; registration with that role returns 400.</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>An approval authority must not be creatable by anyone.</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Not yet — needs a live test on real MongoDB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
-  <conditionalFormatting sqref="G2:G29">
+  <autoFilter ref="A1:G40"/>
+  <conditionalFormatting sqref="G2:G40">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>LEFT($G2,3)="Yes"</formula>
     </cfRule>
@@ -5612,4 +7472,485 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Proposal promise</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>What exists today</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Gap / next step</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Tracker section</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Extract data and cross-verify name, SSN, income, address</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Built, with gaps</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Name, income, employer, SSN last-4, business name, revenue, plus cross-document deposit and payroll-math checks</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Address is not compared; SSN is last-4 only</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>5, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Confidence scoring with human-in-the-loop routing</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Low-confidence extractions are flagged for review, never guessed</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Exceptions dashboard</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Action Needed list and page; flags show in the application list</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Officer is the final approver</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Loan officer and underwriter decision workflow with an audit trail</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Notifications, appeals, real minimum credit scores</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>RAG Q&amp;A with citations for officers and borrowers (web)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Built, not true RAG</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Policy corpus grounded answers with citations; chat also navigates to pages</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Vector search and per-tenant retrieval; policy page with highlighting</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>6, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>RAG on WhatsApp</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Webhook, routing into the assistant, outbound replies</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Missing-document detection with one-click borrower email</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Detection built</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>In-app self-service re-upload replaces the email</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Email notification not built</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>13, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>"Binder dump": auto-split and classify large mixed PDFs (200–500 pages)</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>One upload is one document</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Page splitting, page-level classification, progress</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>TILA / RESPA disclosure-timing checks</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Rules and data model</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>MISMO JSON output for LOS integration</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Phase 3 of the submission</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Complete audit trail of every extraction and decision</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Decisions, referrals and credit-score entries are logged; superseded documents kept</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Log uploads and extractions</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>18, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>GLBA / SOC 2-aligned controls</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Role-based access; private file storage (R2)</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Encryption at rest, zero-retention LLM terms, access logging</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Multi-tenant SaaS, per-bank policy indexing</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Single bank</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>RAG plan phase P2</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Residential / consumer loans with 1003 / URLA</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Different scope</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Auto, personal and small-business loans</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>State the scope change in the pitch</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Azure Document AI / FastAPI / React / vector DB</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Different stack</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Claude vision, Node / Express, Expo, no vector DB yet</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Document the deviation; confirm approved cloud with ThoughtFocus (Rovo Q01)</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Added beyond the proposal</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Small-business vertical, self-service live exceptions, payroll-math and deposit checks, affordability warning, underwriter exception workflow, mock-AI mode</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Lead the pitch with the exception and fraud-signal story</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>5, 13, 18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E17"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal vs Built" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$189</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Proposal vs Built'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,7 +647,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Khavya Sakthivel &amp; Sukumar Dhandapani (Development) · Souvik Das (QA) — updated 2026-10-22 (sections 18–20 added)</t>
+          <t>Khavya Sakthivel &amp; Sukumar Dhandapani (Development) · Souvik Das (QA) — updated 2026-10-24 (identity / credit simulation added)</t>
         </is>
       </c>
     </row>
@@ -705,15 +705,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -764,15 +764,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A18,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A18,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A18,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A18,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A18,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A18,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -787,15 +787,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A19,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A19,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A19,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A19,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A19,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A19,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -810,15 +810,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A20,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A20,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A20,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A20,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A20,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A20,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -833,15 +833,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A21,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A21,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A21,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A21,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A21,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A21,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -856,15 +856,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A22,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A22,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A22,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A22,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A22,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A22,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -879,15 +879,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A23,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A23,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A23,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A23,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A23,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A23,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -902,15 +902,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A24,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A24,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A24,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A24,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A24,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A24,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -925,15 +925,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A25,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A25,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A25,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A25,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A25,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A25,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -948,15 +948,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A26,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A26,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A26,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A26,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A26,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A26,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -971,15 +971,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A27,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A27,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A27,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A27,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A27,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A27,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -994,15 +994,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A28,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A28,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A28,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A28,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A28,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A28,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1017,15 +1017,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A29,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A29,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A29,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A29,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A29,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A29,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A30,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A30,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A30,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A30,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A30,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A30,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1063,15 +1063,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A31,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A31,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A31,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A31,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A31,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A31,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1086,15 +1086,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A32,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A32,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A32,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A32,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A32,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A32,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1109,15 +1109,15 @@
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A33,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A33,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A33,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A33,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A33,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A33,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E33">
@@ -1132,15 +1132,15 @@
         </is>
       </c>
       <c r="B34">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A34,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A34,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A34,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A34,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A34,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A34,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E34">
@@ -1155,15 +1155,15 @@
         </is>
       </c>
       <c r="B35">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A35,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A35,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A35,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A35,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A35,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A35,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E35">
@@ -1178,15 +1178,15 @@
         </is>
       </c>
       <c r="B36">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A36,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A36,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A36,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A36,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A36,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A36,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E36">
@@ -1201,15 +1201,15 @@
         </is>
       </c>
       <c r="B37">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A37,Tasks!$D$2:$D$189,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A37,Tasks!$D$2:$D$202,"Completed")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A37,Tasks!$D$2:$D$189,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A37,Tasks!$D$2:$D$202,"In Progress")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>COUNTIFS(Tasks!$B$2:$B$189,$A37,Tasks!$D$2:$D$189,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$202,$A37,Tasks!$D$2:$D$202,"Not Started")</f>
         <v/>
       </c>
       <c r="E37">
@@ -1231,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NEEDS REAL-TIME API KEY + FUNDING — vendor options: Persona, Onfido, Jumio, ID.me (liveness + barcode/MRZ check)</t>
+          <t>NEEDS REAL-TIME API KEY + FUNDING — vendor options: Persona, Onfido, Jumio, ID.me (liveness + barcode/MRZ check) [2026-10-24] Document-based part built: the licence is now checked for expiry, date of birth and address against the application (real checks on the upload). The vendor ID / selfie / liveness check is still not built.</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FREE — U.S. Treasury OFAC SDN list is a public, free, downloadable dataset; no paid vendor required to build a basic screen</t>
+          <t>FREE — U.S. Treasury OFAC SDN list is a public, free, downloadable dataset; no paid vendor required to build a basic screen [2026-10-24] A SIMULATED sanctions screen exists (scripted test records); the real OFAC list is not loaded.</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FREE TIER AVAILABLE — USPS Web Tools API has a no-cost tier suitable for this use case</t>
+          <t>FREE TIER AVAILABLE — USPS Web Tools API has a no-cost tier suitable for this use case [2026-10-24] Document-level address check built (licence address vs application). USPS deliverability is still not built.</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NEEDS FUNDING — real bureau access (Equifax/Experian/TransUnion) requires a licensed FCRA "permissible purpose" relationship, not just an API key; soft-pull aggregators (Array, Bloom Credit, MeridianLink) are the realistic funded path [2026-10-22] Interim: staff enter the credit score by hand on the Decision page (Section 18).</t>
+          <t>NEEDS FUNDING — real bureau access (Equifax/Experian/TransUnion) requires a licensed FCRA "permissible purpose" relationship, not just an API key; soft-pull aggregators (Array, Bloom Credit, MeridianLink) are the realistic funded path [2026-10-22] Interim: staff enter the credit score by hand on the Decision page (Section 18). [2026-10-24] A SIMULATED credit pull (scripted test records) is built and feeds the decision workflow. A real bureau still needs a contract, consent flow and FCRA permissible purpose.</t>
         </is>
       </c>
     </row>
@@ -6015,9 +6015,334 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Simulated bureau: SSN / name / date-of-birth match, sanctions screening and credit report from scripted test records</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>services/simulatedBureau.js, config/testPersonas.js; route POST /applications/:id/verify. Labelled "Simulated" in the UI and audit trail. A real provider replaces one call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Driver's licence checks on upload: expiry, date of birth and address vs the application</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Real checks, not simulated. Expired ID is a mismatch (borrower must re-upload); an address difference is only a warning. Extraction prompts now read dateOfBirth, licenseNumber, licenseExpiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Five jury test borrowers with pre-loaded documents: Priya (clean), Arjun (low score), Rohan (SSN mismatch), Meera (expired ID), Kavya (no credit history)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>services/seedData.js; documents from data/seed/generate_persona_documents.py. Walkthrough in docs/SIMULATED_VERIFICATION.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Decision page: "Run identity and credit checks" card; identity and sanctions are non-waivable parameters</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Nothing can be approved or referred until the checks have been run. A score can still be typed in by hand (thin-file borrowers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Shared seed module for `npm run seed` and /admin/reset (previously two copies)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>services/seedData.js. Arjun Mehta now ships with his documents pre-loaded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Unit tests for the five stories and the licence checks</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>backend/test/simulated/personas.test.js — 11 tests, real seed data through real code, no database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Click-through of the five stories on real MongoDB after npm run reset</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Only unit tests and a mock API so far (Rohan and Meera previewed in the browser).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Add the five identity / credit stories to DEMO_SCRIPT.md</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Suggested order is in docs/SIMULATED_VERIFICATION.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Replace the simulated bureau with a real provider adapter</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>NEEDS FUNDING / CONTRACT — credit bureau or reseller, SSN match / identity network, sanctions list. Needs the borrower consent flow and FCRA permissible purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Citizenship / residency status field and the product rules that use it</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>US lenders rarely verify citizenship; they verify identity (CIP) and apply product policy to residency. Needs a policy decision first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Store the SSN securely (encrypted or keyed hash) instead of last four digits only</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Required before any real bureau pull; also feeds duplicate detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Detect the same SSN used on more than one application</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>RAG plan edge case E01 (duplicate customers / fraud ring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Soft vs hard credit-pull disclosure wording in the consent step</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Current consent only says credit pull is authorised.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F189"/>
-  <conditionalFormatting sqref="D2:D189">
+  <autoFilter ref="A1:F202"/>
+  <conditionalFormatting sqref="D2:D202">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -6029,7 +6354,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D189" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6043,7 +6368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7457,9 +7782,219 @@
         </is>
       </c>
     </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Identity and credit</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Clean borrower (Priya Nair) passes everything</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Log in as the loan officer, open Priya Nair &gt; Decision, run the identity and credit checks.</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Identity verified, sanctions clear, score 742; every parameter is Met and Approve is enabled.</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>The happy path the other stories are compared against.</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit test on the real seed data; not on real MongoDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Identity and credit</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Low credit score (Arjun Mehta) routes to the exception path</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Run the checks on Arjun Mehta.</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Score 598 vs 620: credit score is Not Met, Approve is disabled, Refer to underwriter is enabled.</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Shows the bank can lend outside its parameters, but only through a named senior role.</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit test on the real seed data; not on real MongoDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Identity and credit</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>SSN that belongs to a different person (Rohan Desai) fails identity</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>Run the checks on Rohan Desai.</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>Identity Failed, credit report Skipped, parameter Not Met, no referral possible. The other person is never named.</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>Catches a mistyped, stolen or synthetic identity even when the documents look perfect.</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit test; also previewed in the browser against a mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Identity and credit</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Expired driver licence (Meera Iyer) is rejected on upload</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Open Meera Iyer &gt; Action Needed (no simulation involved).</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Drivers License shows an "ID expiry" mismatch with a Re-upload button; the bureau result itself is clean.</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>A real document check that works on any upload.</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit test; also previewed in the browser against a mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Identity and credit</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Borrower with no credit history (Kavya Reddy) cannot proceed automatically</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Run the checks on Kavya Reddy.</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Credit report says no history (thin file); credit score stays "Needs entry"; neither approval nor referral is possible until a score is entered by hand or the file is declined.</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>The system refuses to guess a score it does not have.</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit test on the real seed data; not on real MongoDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Identity and credit</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Nothing is approvable until the checks are run</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Open any seeded borrower and look at the Decision page before running the checks.</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Identity, sanctions and credit parameters read "Needs entry"; Approve and Refer are disabled.</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>Prevents a decision on an unverified identity.</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit test; previewed in the browser against a mock API</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G40"/>
-  <conditionalFormatting sqref="G2:G40">
+  <autoFilter ref="A1:G46"/>
+  <conditionalFormatting sqref="G2:G46">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>LEFT($G2,3)="Yes"</formula>
     </cfRule>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -636,7 +636,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -658,7 +657,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
@@ -673,7 +671,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -721,8 +718,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -4906,12 +4901,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sheet added 2026-10-22; keep it current so the demo never claims an unbuilt feature.</t>
+          <t>Sheet added 2026-10-22; keep it current so the demo never claims an unbuilt feature. [2026-10-24] Sheet "Proposal vs Built" is in this workbook; revisit when features land.</t>
         </is>
       </c>
     </row>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -5226,12 +5226,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Arjun Mehta (score 598): officer cannot approve, refers, underwriter approves with an exception, borrower sees only the outcome.</t>
+          <t>Arjun Mehta (score 598): officer cannot approve, refers, underwriter approves with an exception, borrower sees only the outcome. [2026-10-24] Added as "Act 2" in docs/DEMO_SCRIPT.md (five stories, exception walk-through, jury Q&amp;A).</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Suggested order is in docs/SIMULATED_VERIFICATION.md.</t>
+          <t>Suggested order is in docs/SIMULATED_VERIFICATION.md. [2026-10-24] Added as "Act 2" in docs/DEMO_SCRIPT.md (five stories, exception walk-through, jury Q&amp;A).</t>
         </is>
       </c>
     </row>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal vs Built" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Scenarios'!$A$1:$G$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Proposal vs Built'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Khavya Sakthivel &amp; Sukumar Dhandapani (Development) · Souvik Das (QA) — updated 2026-10-24 (identity / credit simulation added)</t>
+          <t>Khavya Sakthivel &amp; Sukumar Dhandapani (Development) · Souvik Das (QA) — updated 2026-10-24 (identity, credit, residency and duplicate checks added)</t>
         </is>
       </c>
     </row>
@@ -702,15 +702,15 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF(Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="D13" s="7">
@@ -759,15 +759,15 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A18,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A18,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A18,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A18,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A18,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A18,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -782,15 +782,15 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A19,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A19,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A19,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A19,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A19,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A19,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -805,15 +805,15 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A20,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A20,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A20,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A20,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A20,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A20,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E20" s="10">
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A21,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A21,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A21,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A21,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A21,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A21,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E21" s="10">
@@ -851,15 +851,15 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A22,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A22,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A22,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A22,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A22,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A22,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E22" s="10">
@@ -874,15 +874,15 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A23,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A23,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A23,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A23,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A23,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A23,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E23" s="10">
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A24,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A24,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A24,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A24,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A24,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A24,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E24" s="10">
@@ -920,15 +920,15 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A25,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A25,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A25,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A25,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A25,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A25,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E25" s="10">
@@ -943,15 +943,15 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A26,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A26,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A26,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A26,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A26,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A26,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E26" s="10">
@@ -966,15 +966,15 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A27,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A27,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A27,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A27,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A27,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A27,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E27" s="10">
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A28,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A28,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A28,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A28,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A28,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A28,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E28" s="10">
@@ -1012,15 +1012,15 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A29,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A29,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A29,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A29,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A29,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A29,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E29" s="10">
@@ -1035,15 +1035,15 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A30,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A30,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A30,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A30,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A30,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A30,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E30" s="10">
@@ -1058,15 +1058,15 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A31,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A31,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A31,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A31,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A31,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A31,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E31" s="10">
@@ -1081,15 +1081,15 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A32,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A32,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A32,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A32,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A32,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A32,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E32" s="10">
@@ -1104,15 +1104,15 @@
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A33,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A33,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A33,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A33,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A33,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A33,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E33">
@@ -1127,15 +1127,15 @@
         </is>
       </c>
       <c r="B34">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A34,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A34,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A34,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A34,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A34,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A34,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E34">
@@ -1150,15 +1150,15 @@
         </is>
       </c>
       <c r="B35">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A35,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A35,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A35,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A35,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A35,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A35,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E35">
@@ -1173,15 +1173,15 @@
         </is>
       </c>
       <c r="B36">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A36,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A36,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A36,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A36,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A36,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A36,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E36">
@@ -1196,15 +1196,15 @@
         </is>
       </c>
       <c r="B37">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A37,Tasks!$D$2:$D$202,"Completed")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A37,Tasks!$D$2:$D$209,"Completed")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A37,Tasks!$D$2:$D$202,"In Progress")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A37,Tasks!$D$2:$D$209,"In Progress")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>COUNTIFS(Tasks!$B$2:$B$202,$A37,Tasks!$D$2:$D$202,"Not Started")</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$209,$A37,Tasks!$D$2:$D$209,"Not Started")</f>
         <v/>
       </c>
       <c r="E37">
@@ -1226,7 +1226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Only unit tests and a mock API so far (Rohan and Meera previewed in the browser).</t>
+          <t>Only unit tests and a mock API so far (Rohan and Meera previewed in the browser). [2026-10-24] Now seven stories: Anil Kapoor (reused identity) and Lakshmi Pillai (visa ends before the loan) were added.</t>
         </is>
       </c>
     </row>
@@ -6251,12 +6251,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>US lenders rarely verify citizenship; they verify identity (CIP) and apply product policy to residency. Needs a policy decision first.</t>
+          <t>US lenders rarely verify citizenship; they verify identity (CIP) and apply product policy to residency. Needs a policy decision first. [2026-10-24] Built: applicants declare U.S. citizen / permanent resident / visa holder (+ visa expiry); rule in services/residency.js — a visa must outlast the loan term, otherwise an underwriter may waive it with a condition. Citizenship is deliberately NOT verified against any government source. Policy text: data/policies/residency-and-identity-policy.md.</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Required before any real bureau pull; also feeds duplicate detection.</t>
+          <t>Required before any real bureau pull; also feeds duplicate detection. [2026-10-24] Now also needed to replace the last-4 + date-of-birth duplicate key.</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>RAG plan edge case E01 (duplicate customers / fraud ring).</t>
+          <t>RAG plan edge case E01 (duplicate customers / fraud ring). [2026-10-24] Built as services/duplicateCheck.js. Key is SSN last-4 + date of birth (a proxy); only the LATER application is flagged; different name = identity reuse, same name = second open application. Never waivable. Replace the key with a keyed hash of the full SSN once it is stored (see the secure-SSN task).</t>
         </is>
       </c>
     </row>
@@ -6335,9 +6335,184 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Residency status on the application form (U.S. citizen / permanent resident / visa holder + visa expiry date) with intake validation</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>NewApplicationScreen.js; validateResidency() in services/residency.js. An expired or missing visa date is rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Residency decision parameter: a visa must outlast the loan term; shortfall is waivable by an underwriter with a condition</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Shown on the Decision page; Lakshmi Pillai is the demo borrower. Missing residency data is pending, never met.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Duplicate-identity decision parameter and "Matching earlier applications" panel on the Decision page</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Staff see who the earlier application belongs to and can open it. Seeded borrowers are created in order so Anil Kapoor (later) is flagged and Priya Nair (original) is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Policy: one open application per applicant, and how reused identities are handled</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>data/policies/residency-and-identity-policy.md (also covers who may apply, visa holders, how identity is verified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Two more jury borrowers with pre-loaded documents: Anil Kapoor (reused identity) and Lakshmi Pillai (visa holder)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Seven stories in total — see docs/SIMULATED_VERIFICATION.md and DEMO_SCRIPT.md Act 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Unit tests for duplicate matching, residency and the two new stories</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>backend/test/simulated/residencyAndDuplicates.test.js — 15 tests. Full backend suite: 86 tests, 85 pass (the 1 failure, test/rag/serviceClients.test.js, predates this work).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>17. Identity, Address &amp; Credit Verification (KYC / Underwriting)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ingest the new residency-and-identity policy file into the policy store so the assistant can quote it</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>npm run ingest (Mongo) or /admin/ingest-chroma (Chroma). The file is in the repo but not yet indexed anywhere.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F202"/>
-  <conditionalFormatting sqref="D2:D202">
+  <autoFilter ref="A1:F209"/>
+  <conditionalFormatting sqref="D2:D209">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Completed"</formula>
     </cfRule>
@@ -6349,7 +6524,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Completed,In Progress,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6363,7 +6538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7987,9 +8162,114 @@
         </is>
       </c>
     </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate identity</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>A later application that reuses an earlier applicant's SSN last-4 and date of birth is stopped (Anil Kapoor)</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>Open Anil Kapoor &gt; Decision as the loan officer (do not run any checks first).</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>"No duplicate or reused identity" is Not Met with a "Matching earlier applications" panel naming Priya Nair and an Open link. Approval and referral are impossible; an underwriter cannot waive it.</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>Catches identity reuse from the bank's own records, with no outside service.</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit tests on the real seed data; previewed in the browser against a mock API</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate identity</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>The original applicant is not penalised (Priya Nair)</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Open Priya Nair &gt; Decision, run the checks.</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>The duplicate check is Met and Approve is enabled, even though Anil copied her details.</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>A genuine borrower must never be blocked by an impostor.</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit test; not on real MongoDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Residency</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>A visa that ends before the loan can only be approved as an exception (Lakshmi Pillai)</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Open Lakshmi Pillai &gt; Decision, run the checks; then refer and have the underwriter approve waiving "residency" with a condition.</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>"Residency status covers the loan term" is Not Met (visa to 2028-06-30, 36-month term to 2029-10); the officer cannot approve; the underwriter can, with compensating factors and a condition.</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>Shows a practical residency rule without ever verifying citizenship against a government source.</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>Yes — unit tests (including the underwriter approval); previewed in the browser against a mock API</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G46"/>
-  <conditionalFormatting sqref="G2:G46">
+  <autoFilter ref="A1:G49"/>
+  <conditionalFormatting sqref="G2:G49">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>LEFT($G2,3)="Yes"</formula>
     </cfRule>

--- a/docs/LoanLensAI_Development_Task_Tracker.xlsx
+++ b/docs/LoanLensAI_Development_Task_Tracker.xlsx
@@ -5626,12 +5626,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>No edit endpoint or screen exists.</t>
+          <t>PUT /applications/:id (borrower, Submitted/Needs Review only). Non-identity fields; same intake rules; all documents re-verified; every change logged old-&gt;new in review history. Edit button + form in ApplicationDetailScreen. 14 unit tests. FAQ updated: re-run /admin/ingest-chroma.</t>
         </is>
       </c>
     </row>
